--- a/data/key1/proyect5/files/Wide World Importers.xlsx
+++ b/data/key1/proyect5/files/Wide World Importers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asdru\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Teacher Sergio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6E8057D-5951-43EC-899C-C1B76F90AE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43402D9-9188-489C-9F6B-AD0F77901B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="20700" windowHeight="7410" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="3" r:id="rId1"/>
@@ -20,11 +20,22 @@
     <sheet name="Products" sheetId="4" r:id="rId5"/>
     <sheet name="Inventory" sheetId="2" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId7"/>
-    <pivotCache cacheId="18" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2607,7 +2618,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -2700,24 +2711,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2726,12 +2736,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2742,6 +2746,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="40% - Accent1" xfId="3" builtinId="31"/>
@@ -2750,12 +2760,6 @@
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2772,9 +2776,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2784,13 +2785,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2803,7 +2810,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2841,7 +2851,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[SalesData - Proyecto - Wide World Importers.xlsx]Order Analysis!PivotTable3</c:name>
+    <c:name>[Wide World Importers.xlsx]Order Analysis!PivotTable3</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -2944,7 +2954,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-SV"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
@@ -3000,7 +3010,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="es-SV"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
@@ -4850,7 +4860,7 @@
             <c:numRef>
               <c:f>'Order Analysis'!$C$4:$C$198</c:f>
               <c:numCache>
-                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>_-"$"* #,##0.00_-;\-"$"* #,##0.00_-;_-"$"* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="194"/>
                 <c:pt idx="0">
                   <c:v>15.11</c:v>
@@ -5650,6 +5660,7 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -6603,7 +6614,7 @@
         <s v="French-Canadian Sugar Pie"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Unit Price" numFmtId="44">
+    <cacheField name="Unit Price" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.08" maxValue="49.74"/>
     </cacheField>
     <cacheField name="Quantity" numFmtId="0">
@@ -9232,7 +9243,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{73C4A956-0A98-4052-B482-AB5CDC1D0456}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{73C4A956-0A98-4052-B482-AB5CDC1D0456}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A102" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -9666,7 +9677,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAADCA13-36CB-4E2A-857C-9A2669A7025A}" name="PivotTable3" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Customer ID">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAADCA13-36CB-4E2A-857C-9A2669A7025A}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Customer ID">
   <location ref="A3:C198" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -9887,7 +9898,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -10498,7 +10509,7 @@
   </pageFields>
   <dataFields count="2">
     <dataField name="Total Units" fld="5" baseField="2" baseItem="0"/>
-    <dataField name="Total Price" fld="4" baseField="2" baseItem="0" numFmtId="44"/>
+    <dataField name="Total Price" fld="4" baseField="2" baseItem="0" numFmtId="164"/>
   </dataFields>
   <chartFormats count="2">
     <chartFormat chart="7" format="0" series="1">
@@ -10546,15 +10557,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OrdersTable" displayName="OrdersTable" ref="A3:H199" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OrdersTable" displayName="OrdersTable" ref="A3:H199" headerRowDxfId="18">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Order ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order Date" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Customer ID" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Order ID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order Date" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Customer ID" dataDxfId="15"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Product"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Unit Price" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Quantity" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Discount" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Unit Price" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Quantity" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Discount" dataDxfId="12"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Region"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10562,34 +10573,34 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2B1A53F8-A39F-4C02-B164-EEA1F52574CE}" name="Table25" displayName="Table25" ref="A3:B83" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2B1A53F8-A39F-4C02-B164-EEA1F52574CE}" name="Table25" displayName="Table25" ref="A3:B83" totalsRowShown="0" headerRowDxfId="11">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{AF538A8F-098A-45C3-BFBD-B77A585C8F8B}" name="Product"/>
-    <tableColumn id="2" xr3:uid="{25F38738-0ABE-454D-B674-15131639985A}" name="Unit Price" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{25F38738-0ABE-454D-B674-15131639985A}" name="Unit Price" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EC7181DC-78EB-4F0D-A152-8E81FE2530D8}" name="Table257" displayName="Table257" ref="D3:E83" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EC7181DC-78EB-4F0D-A152-8E81FE2530D8}" name="Table257" displayName="Table257" ref="D3:E83" totalsRowShown="0" headerRowDxfId="9">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{ACF17F78-FD68-4AE4-B602-A29A8D8CFB59}" name="Product"/>
-    <tableColumn id="2" xr3:uid="{BAEA0B5B-3717-4873-A605-4231095D9965}" name="Unit Price" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{BAEA0B5B-3717-4873-A605-4231095D9965}" name="Unit Price" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41433919-C7EC-4C8C-A995-AE7259D9DBC0}" name="Table2" displayName="Table2" ref="A3:F80" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41433919-C7EC-4C8C-A995-AE7259D9DBC0}" name="Table2" displayName="Table2" ref="A3:F80" totalsRowShown="0" headerRowDxfId="7">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{763562AD-1F50-4801-BE6D-6A57B2688737}" name="ID"/>
     <tableColumn id="2" xr3:uid="{D2643E02-B33E-4CF0-982F-0C0D4E3242BE}" name="Product Name"/>
-    <tableColumn id="3" xr3:uid="{BBC73D59-D513-4893-A1B1-8210CF4ACF5F}" name="Unit Price" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{C8934059-E678-40FC-BAF4-D911C1E803C2}" name="In Stock" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{629EE812-B522-490B-A09C-8C606E2E447B}" name="On Order" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{AFE626F5-90E0-4B8A-8E95-6F2F9A064DD1}" name="Discontinued" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{BBC73D59-D513-4893-A1B1-8210CF4ACF5F}" name="Unit Price" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{C8934059-E678-40FC-BAF4-D911C1E803C2}" name="In Stock" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{629EE812-B522-490B-A09C-8C606E2E447B}" name="On Order" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{AFE626F5-90E0-4B8A-8E95-6F2F9A064DD1}" name="Discontinued" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10881,29 +10892,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD96B423-F0CF-48AC-BF42-DFD5442CB7E7}">
   <dimension ref="A1:E94"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>414</v>
       </c>
@@ -10920,7 +10931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>572</v>
       </c>
@@ -10937,7 +10948,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>577</v>
       </c>
@@ -10954,7 +10965,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>582</v>
       </c>
@@ -10971,7 +10982,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>585</v>
       </c>
@@ -10988,7 +10999,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>589</v>
       </c>
@@ -11005,7 +11016,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>593</v>
       </c>
@@ -11022,7 +11033,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>596</v>
       </c>
@@ -11039,7 +11050,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>601</v>
       </c>
@@ -11056,7 +11067,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>605</v>
       </c>
@@ -11073,7 +11084,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>607</v>
       </c>
@@ -11090,7 +11101,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>609</v>
       </c>
@@ -11107,7 +11118,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>611</v>
       </c>
@@ -11124,7 +11135,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>613</v>
       </c>
@@ -11141,7 +11152,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>615</v>
       </c>
@@ -11158,7 +11169,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>617</v>
       </c>
@@ -11175,7 +11186,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>619</v>
       </c>
@@ -11192,7 +11203,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>621</v>
       </c>
@@ -11209,7 +11220,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>623</v>
       </c>
@@ -11226,7 +11237,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>625</v>
       </c>
@@ -11243,7 +11254,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>627</v>
       </c>
@@ -11260,7 +11271,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>629</v>
       </c>
@@ -11277,7 +11288,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>631</v>
       </c>
@@ -11294,7 +11305,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>633</v>
       </c>
@@ -11311,7 +11322,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>635</v>
       </c>
@@ -11328,7 +11339,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>637</v>
       </c>
@@ -11345,7 +11356,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>639</v>
       </c>
@@ -11362,7 +11373,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>641</v>
       </c>
@@ -11379,7 +11390,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>643</v>
       </c>
@@ -11396,7 +11407,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>645</v>
       </c>
@@ -11413,7 +11424,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>647</v>
       </c>
@@ -11430,7 +11441,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>649</v>
       </c>
@@ -11447,7 +11458,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>651</v>
       </c>
@@ -11464,7 +11475,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>653</v>
       </c>
@@ -11481,7 +11492,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>655</v>
       </c>
@@ -11498,7 +11509,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>657</v>
       </c>
@@ -11515,7 +11526,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>659</v>
       </c>
@@ -11532,7 +11543,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>661</v>
       </c>
@@ -11549,7 +11560,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>663</v>
       </c>
@@ -11566,7 +11577,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>665</v>
       </c>
@@ -11583,7 +11594,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>667</v>
       </c>
@@ -11600,7 +11611,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>669</v>
       </c>
@@ -11617,7 +11628,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>671</v>
       </c>
@@ -11634,7 +11645,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>673</v>
       </c>
@@ -11651,7 +11662,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>675</v>
       </c>
@@ -11668,7 +11679,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>677</v>
       </c>
@@ -11685,7 +11696,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>679</v>
       </c>
@@ -11702,7 +11713,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>681</v>
       </c>
@@ -11719,7 +11730,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>683</v>
       </c>
@@ -11736,7 +11747,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>685</v>
       </c>
@@ -11753,7 +11764,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>687</v>
       </c>
@@ -11770,7 +11781,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>689</v>
       </c>
@@ -11787,7 +11798,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>691</v>
       </c>
@@ -11804,7 +11815,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>693</v>
       </c>
@@ -11821,7 +11832,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>695</v>
       </c>
@@ -11838,7 +11849,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>697</v>
       </c>
@@ -11855,7 +11866,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>699</v>
       </c>
@@ -11872,7 +11883,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>701</v>
       </c>
@@ -11889,7 +11900,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>703</v>
       </c>
@@ -11906,7 +11917,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>705</v>
       </c>
@@ -11923,7 +11934,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>707</v>
       </c>
@@ -11940,7 +11951,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>709</v>
       </c>
@@ -11957,7 +11968,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>711</v>
       </c>
@@ -11974,7 +11985,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>713</v>
       </c>
@@ -11991,7 +12002,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>715</v>
       </c>
@@ -12008,7 +12019,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>717</v>
       </c>
@@ -12025,7 +12036,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>719</v>
       </c>
@@ -12042,7 +12053,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>721</v>
       </c>
@@ -12059,7 +12070,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>723</v>
       </c>
@@ -12076,7 +12087,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>725</v>
       </c>
@@ -12093,7 +12104,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>727</v>
       </c>
@@ -12110,7 +12121,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>729</v>
       </c>
@@ -12127,7 +12138,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>731</v>
       </c>
@@ -12144,7 +12155,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>733</v>
       </c>
@@ -12161,7 +12172,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>735</v>
       </c>
@@ -12178,7 +12189,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>737</v>
       </c>
@@ -12195,7 +12206,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>739</v>
       </c>
@@ -12212,7 +12223,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>741</v>
       </c>
@@ -12229,7 +12240,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>743</v>
       </c>
@@ -12246,7 +12257,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>745</v>
       </c>
@@ -12263,7 +12274,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>747</v>
       </c>
@@ -12280,7 +12291,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>749</v>
       </c>
@@ -12297,7 +12308,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>751</v>
       </c>
@@ -12314,7 +12325,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>753</v>
       </c>
@@ -12331,7 +12342,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>755</v>
       </c>
@@ -12348,7 +12359,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>757</v>
       </c>
@@ -12365,7 +12376,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>759</v>
       </c>
@@ -12382,7 +12393,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>761</v>
       </c>
@@ -12399,7 +12410,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>763</v>
       </c>
@@ -12416,7 +12427,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>765</v>
       </c>
@@ -12433,7 +12444,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>767</v>
       </c>
@@ -12450,7 +12461,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>769</v>
       </c>
@@ -12481,520 +12492,520 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05BB64E2-AFCF-4FD5-83BF-FD2D6759A573}">
   <dimension ref="A1:C102"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-    </row>
-    <row r="2" spans="1:3" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+    </row>
+    <row r="2" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="17" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="17" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="17" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="17" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="17" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="17" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="17" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="17" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="17" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="16" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="17" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="17" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="17" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="17" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="17" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="17" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="17" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="17" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="17" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="17" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="17" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="17" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="16" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="17" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="17" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="17" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="17" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="14" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="17" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="17" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="17" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="17" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="17" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="14" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="17" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="17" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="14" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="16" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="17" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="17" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="17" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="14" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="17" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="14" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="17" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="14" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="17" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="14" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="17" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="14" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="17" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="14" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="17" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="14" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="17" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="17" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="14" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="16" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="17" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="17" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="14" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="17" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="14" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="17" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="17" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="14" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="17" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="14" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="17" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="14" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="17" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="14" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="17" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="14" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="17" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="14" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="17" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="14" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="16" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="13" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="17" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="14" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="17" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="14" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="17" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="14" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="17" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="14" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="17" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="14" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="17" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="14" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="17" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="14" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="17" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="14" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="17" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="14" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="17" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="14" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="17" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="14" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="17" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="14" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="16" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="13" t="s">
         <v>852</v>
       </c>
     </row>
@@ -13006,37 +13017,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H199"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -13049,7 +13060,7 @@
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -13058,11 +13069,11 @@
       <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>10260</v>
       </c>
@@ -13081,11 +13092,11 @@
       <c r="F4" s="1">
         <v>68</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>10261</v>
       </c>
@@ -13104,11 +13115,11 @@
       <c r="F5" s="1">
         <v>78</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>10262</v>
       </c>
@@ -13127,11 +13138,11 @@
       <c r="F6" s="1">
         <v>93</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>10263</v>
       </c>
@@ -13150,11 +13161,11 @@
       <c r="F7" s="1">
         <v>85</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>10264</v>
       </c>
@@ -13173,11 +13184,11 @@
       <c r="F8" s="1">
         <v>104</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>10265</v>
       </c>
@@ -13196,11 +13207,11 @@
       <c r="F9" s="1">
         <v>97</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>10266</v>
       </c>
@@ -13219,11 +13230,11 @@
       <c r="F10" s="1">
         <v>69</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10267</v>
       </c>
@@ -13242,11 +13253,11 @@
       <c r="F11" s="1">
         <v>86</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10268</v>
       </c>
@@ -13265,11 +13276,11 @@
       <c r="F12" s="1">
         <v>94</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10269</v>
       </c>
@@ -13288,11 +13299,11 @@
       <c r="F13" s="1">
         <v>87</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10270</v>
       </c>
@@ -13311,11 +13322,11 @@
       <c r="F14" s="1">
         <v>65</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>10271</v>
       </c>
@@ -13334,11 +13345,11 @@
       <c r="F15" s="1">
         <v>86</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>10272</v>
       </c>
@@ -13357,11 +13368,11 @@
       <c r="F16" s="1">
         <v>99</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>10273</v>
       </c>
@@ -13380,11 +13391,11 @@
       <c r="F17" s="1">
         <v>81</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>10274</v>
       </c>
@@ -13403,11 +13414,11 @@
       <c r="F18" s="1">
         <v>62</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>10275</v>
       </c>
@@ -13426,11 +13437,11 @@
       <c r="F19" s="1">
         <v>53</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>10276</v>
       </c>
@@ -13449,11 +13460,11 @@
       <c r="F20" s="1">
         <v>106</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>10277</v>
       </c>
@@ -13472,11 +13483,11 @@
       <c r="F21" s="1">
         <v>111</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>10278</v>
       </c>
@@ -13495,11 +13506,11 @@
       <c r="F22" s="1">
         <v>103</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>10279</v>
       </c>
@@ -13518,11 +13529,11 @@
       <c r="F23" s="1">
         <v>85</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>10280</v>
       </c>
@@ -13541,11 +13552,11 @@
       <c r="F24" s="1">
         <v>108</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>10281</v>
       </c>
@@ -13564,11 +13575,11 @@
       <c r="F25" s="1">
         <v>106</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>10282</v>
       </c>
@@ -13587,11 +13598,11 @@
       <c r="F26" s="1">
         <v>55</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>10283</v>
       </c>
@@ -13610,11 +13621,11 @@
       <c r="F27" s="1">
         <v>95</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>10284</v>
       </c>
@@ -13633,11 +13644,11 @@
       <c r="F28" s="1">
         <v>50</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>10285</v>
       </c>
@@ -13656,11 +13667,11 @@
       <c r="F29" s="1">
         <v>117</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>10286</v>
       </c>
@@ -13679,11 +13690,11 @@
       <c r="F30" s="1">
         <v>111</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>10287</v>
       </c>
@@ -13702,11 +13713,11 @@
       <c r="F31" s="1">
         <v>50</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>10288</v>
       </c>
@@ -13725,11 +13736,11 @@
       <c r="F32" s="1">
         <v>71</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>10289</v>
       </c>
@@ -13748,11 +13759,11 @@
       <c r="F33" s="1">
         <v>68</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>10290</v>
       </c>
@@ -13771,11 +13782,11 @@
       <c r="F34" s="1">
         <v>83</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>10291</v>
       </c>
@@ -13794,11 +13805,11 @@
       <c r="F35" s="1">
         <v>117</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>10292</v>
       </c>
@@ -13817,11 +13828,11 @@
       <c r="F36" s="1">
         <v>105</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>10293</v>
       </c>
@@ -13840,11 +13851,11 @@
       <c r="F37" s="1">
         <v>103</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>10294</v>
       </c>
@@ -13863,11 +13874,11 @@
       <c r="F38" s="1">
         <v>120</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>10295</v>
       </c>
@@ -13886,11 +13897,11 @@
       <c r="F39" s="1">
         <v>105</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>10296</v>
       </c>
@@ -13909,11 +13920,11 @@
       <c r="F40" s="1">
         <v>115</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>10297</v>
       </c>
@@ -13932,11 +13943,11 @@
       <c r="F41" s="1">
         <v>90</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>10298</v>
       </c>
@@ -13955,11 +13966,11 @@
       <c r="F42" s="1">
         <v>70</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>10299</v>
       </c>
@@ -13978,11 +13989,11 @@
       <c r="F43" s="1">
         <v>98</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>10300</v>
       </c>
@@ -14001,11 +14012,11 @@
       <c r="F44" s="1">
         <v>50</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>10301</v>
       </c>
@@ -14024,11 +14035,11 @@
       <c r="F45" s="1">
         <v>98</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>10302</v>
       </c>
@@ -14047,11 +14058,11 @@
       <c r="F46" s="1">
         <v>63</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>10303</v>
       </c>
@@ -14070,11 +14081,11 @@
       <c r="F47" s="1">
         <v>70</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G47" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>10304</v>
       </c>
@@ -14093,11 +14104,11 @@
       <c r="F48" s="1">
         <v>63</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G48" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>10305</v>
       </c>
@@ -14116,11 +14127,11 @@
       <c r="F49" s="1">
         <v>92</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G49" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>10306</v>
       </c>
@@ -14139,11 +14150,11 @@
       <c r="F50" s="1">
         <v>108</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G50" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>10307</v>
       </c>
@@ -14162,11 +14173,11 @@
       <c r="F51" s="1">
         <v>82</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G51" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>10308</v>
       </c>
@@ -14185,11 +14196,11 @@
       <c r="F52" s="1">
         <v>57</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>10309</v>
       </c>
@@ -14208,11 +14219,11 @@
       <c r="F53" s="1">
         <v>115</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G53" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>10310</v>
       </c>
@@ -14231,11 +14242,11 @@
       <c r="F54" s="1">
         <v>94</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G54" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>10311</v>
       </c>
@@ -14254,11 +14265,11 @@
       <c r="F55" s="1">
         <v>102</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G55" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>10312</v>
       </c>
@@ -14277,11 +14288,11 @@
       <c r="F56" s="1">
         <v>103</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G56" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>10313</v>
       </c>
@@ -14300,11 +14311,11 @@
       <c r="F57" s="1">
         <v>82</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>10314</v>
       </c>
@@ -14323,11 +14334,11 @@
       <c r="F58" s="1">
         <v>63</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>10315</v>
       </c>
@@ -14346,11 +14357,11 @@
       <c r="F59" s="1">
         <v>64</v>
       </c>
-      <c r="G59" s="4">
+      <c r="G59" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>10316</v>
       </c>
@@ -14369,11 +14380,11 @@
       <c r="F60" s="1">
         <v>102</v>
       </c>
-      <c r="G60" s="4">
+      <c r="G60" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>10317</v>
       </c>
@@ -14392,11 +14403,11 @@
       <c r="F61" s="1">
         <v>92</v>
       </c>
-      <c r="G61" s="4">
+      <c r="G61" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>10318</v>
       </c>
@@ -14415,11 +14426,11 @@
       <c r="F62" s="1">
         <v>97</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G62" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>10319</v>
       </c>
@@ -14438,11 +14449,11 @@
       <c r="F63" s="1">
         <v>86</v>
       </c>
-      <c r="G63" s="4">
+      <c r="G63" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>10320</v>
       </c>
@@ -14461,11 +14472,11 @@
       <c r="F64" s="1">
         <v>115</v>
       </c>
-      <c r="G64" s="4">
+      <c r="G64" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>10321</v>
       </c>
@@ -14484,11 +14495,11 @@
       <c r="F65" s="1">
         <v>73</v>
       </c>
-      <c r="G65" s="4">
+      <c r="G65" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>10322</v>
       </c>
@@ -14507,11 +14518,11 @@
       <c r="F66" s="1">
         <v>118</v>
       </c>
-      <c r="G66" s="4">
+      <c r="G66" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>10323</v>
       </c>
@@ -14530,11 +14541,11 @@
       <c r="F67" s="1">
         <v>67</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G67" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>10324</v>
       </c>
@@ -14553,11 +14564,11 @@
       <c r="F68" s="1">
         <v>76</v>
       </c>
-      <c r="G68" s="4">
+      <c r="G68" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>10325</v>
       </c>
@@ -14576,11 +14587,11 @@
       <c r="F69" s="1">
         <v>111</v>
       </c>
-      <c r="G69" s="4">
+      <c r="G69" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>10326</v>
       </c>
@@ -14599,11 +14610,11 @@
       <c r="F70" s="1">
         <v>99</v>
       </c>
-      <c r="G70" s="4">
+      <c r="G70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>10327</v>
       </c>
@@ -14622,11 +14633,11 @@
       <c r="F71" s="1">
         <v>78</v>
       </c>
-      <c r="G71" s="4">
+      <c r="G71" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>10328</v>
       </c>
@@ -14645,11 +14656,11 @@
       <c r="F72" s="1">
         <v>107</v>
       </c>
-      <c r="G72" s="4">
+      <c r="G72" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>10329</v>
       </c>
@@ -14668,11 +14679,11 @@
       <c r="F73" s="1">
         <v>90</v>
       </c>
-      <c r="G73" s="4">
+      <c r="G73" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>10330</v>
       </c>
@@ -14691,11 +14702,11 @@
       <c r="F74" s="1">
         <v>66</v>
       </c>
-      <c r="G74" s="4">
+      <c r="G74" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>10331</v>
       </c>
@@ -14714,11 +14725,11 @@
       <c r="F75" s="1">
         <v>116</v>
       </c>
-      <c r="G75" s="4">
+      <c r="G75" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>10332</v>
       </c>
@@ -14737,11 +14748,11 @@
       <c r="F76" s="1">
         <v>113</v>
       </c>
-      <c r="G76" s="4">
+      <c r="G76" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>10333</v>
       </c>
@@ -14760,11 +14771,11 @@
       <c r="F77" s="1">
         <v>92</v>
       </c>
-      <c r="G77" s="4">
+      <c r="G77" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>10334</v>
       </c>
@@ -14783,11 +14794,11 @@
       <c r="F78" s="1">
         <v>55</v>
       </c>
-      <c r="G78" s="4">
+      <c r="G78" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>10335</v>
       </c>
@@ -14806,11 +14817,11 @@
       <c r="F79" s="1">
         <v>53</v>
       </c>
-      <c r="G79" s="4">
+      <c r="G79" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>10336</v>
       </c>
@@ -14829,11 +14840,11 @@
       <c r="F80" s="1">
         <v>104</v>
       </c>
-      <c r="G80" s="4">
+      <c r="G80" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>10337</v>
       </c>
@@ -14852,11 +14863,11 @@
       <c r="F81" s="1">
         <v>94</v>
       </c>
-      <c r="G81" s="4">
+      <c r="G81" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>10338</v>
       </c>
@@ -14875,11 +14886,11 @@
       <c r="F82" s="1">
         <v>78</v>
       </c>
-      <c r="G82" s="4">
+      <c r="G82" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>10339</v>
       </c>
@@ -14898,11 +14909,11 @@
       <c r="F83" s="1">
         <v>120</v>
       </c>
-      <c r="G83" s="4">
+      <c r="G83" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>10340</v>
       </c>
@@ -14921,11 +14932,11 @@
       <c r="F84" s="1">
         <v>53</v>
       </c>
-      <c r="G84" s="4">
+      <c r="G84" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>10341</v>
       </c>
@@ -14944,11 +14955,11 @@
       <c r="F85" s="1">
         <v>93</v>
       </c>
-      <c r="G85" s="4">
+      <c r="G85" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>10342</v>
       </c>
@@ -14967,11 +14978,11 @@
       <c r="F86" s="1">
         <v>56</v>
       </c>
-      <c r="G86" s="4">
+      <c r="G86" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>10343</v>
       </c>
@@ -14990,11 +15001,11 @@
       <c r="F87" s="1">
         <v>67</v>
       </c>
-      <c r="G87" s="4">
+      <c r="G87" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>10344</v>
       </c>
@@ -15013,11 +15024,11 @@
       <c r="F88" s="1">
         <v>96</v>
       </c>
-      <c r="G88" s="4">
+      <c r="G88" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>10345</v>
       </c>
@@ -15036,11 +15047,11 @@
       <c r="F89" s="1">
         <v>99</v>
       </c>
-      <c r="G89" s="4">
+      <c r="G89" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>10346</v>
       </c>
@@ -15059,11 +15070,11 @@
       <c r="F90" s="1">
         <v>84</v>
       </c>
-      <c r="G90" s="4">
+      <c r="G90" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>10347</v>
       </c>
@@ -15082,11 +15093,11 @@
       <c r="F91" s="1">
         <v>93</v>
       </c>
-      <c r="G91" s="4">
+      <c r="G91" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>10348</v>
       </c>
@@ -15105,11 +15116,11 @@
       <c r="F92" s="1">
         <v>109</v>
       </c>
-      <c r="G92" s="4">
+      <c r="G92" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>10349</v>
       </c>
@@ -15128,11 +15139,11 @@
       <c r="F93" s="1">
         <v>86</v>
       </c>
-      <c r="G93" s="4">
+      <c r="G93" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>10350</v>
       </c>
@@ -15151,11 +15162,11 @@
       <c r="F94" s="1">
         <v>60</v>
       </c>
-      <c r="G94" s="4">
+      <c r="G94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>10351</v>
       </c>
@@ -15174,11 +15185,11 @@
       <c r="F95" s="1">
         <v>55</v>
       </c>
-      <c r="G95" s="4">
+      <c r="G95" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>10352</v>
       </c>
@@ -15197,11 +15208,11 @@
       <c r="F96" s="1">
         <v>103</v>
       </c>
-      <c r="G96" s="4">
+      <c r="G96" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>10353</v>
       </c>
@@ -15220,11 +15231,11 @@
       <c r="F97" s="1">
         <v>82</v>
       </c>
-      <c r="G97" s="4">
+      <c r="G97" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>10354</v>
       </c>
@@ -15243,11 +15254,11 @@
       <c r="F98" s="1">
         <v>68</v>
       </c>
-      <c r="G98" s="4">
+      <c r="G98" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>10355</v>
       </c>
@@ -15266,11 +15277,11 @@
       <c r="F99" s="1">
         <v>56</v>
       </c>
-      <c r="G99" s="4">
+      <c r="G99" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>10356</v>
       </c>
@@ -15289,11 +15300,11 @@
       <c r="F100" s="1">
         <v>61</v>
       </c>
-      <c r="G100" s="4">
+      <c r="G100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>10357</v>
       </c>
@@ -15312,11 +15323,11 @@
       <c r="F101" s="1">
         <v>111</v>
       </c>
-      <c r="G101" s="4">
+      <c r="G101" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>10358</v>
       </c>
@@ -15335,11 +15346,11 @@
       <c r="F102" s="1">
         <v>93</v>
       </c>
-      <c r="G102" s="4">
+      <c r="G102" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>10359</v>
       </c>
@@ -15358,11 +15369,11 @@
       <c r="F103" s="1">
         <v>54</v>
       </c>
-      <c r="G103" s="4">
+      <c r="G103" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>10360</v>
       </c>
@@ -15381,11 +15392,11 @@
       <c r="F104" s="1">
         <v>97</v>
       </c>
-      <c r="G104" s="4">
+      <c r="G104" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>10361</v>
       </c>
@@ -15404,11 +15415,11 @@
       <c r="F105" s="1">
         <v>111</v>
       </c>
-      <c r="G105" s="4">
+      <c r="G105" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>10362</v>
       </c>
@@ -15427,11 +15438,11 @@
       <c r="F106" s="1">
         <v>86</v>
       </c>
-      <c r="G106" s="4">
+      <c r="G106" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>10363</v>
       </c>
@@ -15450,11 +15461,11 @@
       <c r="F107" s="1">
         <v>98</v>
       </c>
-      <c r="G107" s="4">
+      <c r="G107" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>10364</v>
       </c>
@@ -15473,11 +15484,11 @@
       <c r="F108" s="1">
         <v>110</v>
       </c>
-      <c r="G108" s="4">
+      <c r="G108" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>10365</v>
       </c>
@@ -15496,11 +15507,11 @@
       <c r="F109" s="1">
         <v>76</v>
       </c>
-      <c r="G109" s="4">
+      <c r="G109" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>10366</v>
       </c>
@@ -15519,11 +15530,11 @@
       <c r="F110" s="1">
         <v>115</v>
       </c>
-      <c r="G110" s="4">
+      <c r="G110" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>10367</v>
       </c>
@@ -15542,11 +15553,11 @@
       <c r="F111" s="1">
         <v>66</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G111" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>10368</v>
       </c>
@@ -15565,11 +15576,11 @@
       <c r="F112" s="1">
         <v>86</v>
       </c>
-      <c r="G112" s="4">
+      <c r="G112" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>10369</v>
       </c>
@@ -15588,11 +15599,11 @@
       <c r="F113" s="1">
         <v>103</v>
       </c>
-      <c r="G113" s="4">
+      <c r="G113" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>10370</v>
       </c>
@@ -15611,11 +15622,11 @@
       <c r="F114" s="1">
         <v>97</v>
       </c>
-      <c r="G114" s="4">
+      <c r="G114" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>10371</v>
       </c>
@@ -15634,11 +15645,11 @@
       <c r="F115" s="1">
         <v>89</v>
       </c>
-      <c r="G115" s="4">
+      <c r="G115" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>10372</v>
       </c>
@@ -15657,11 +15668,11 @@
       <c r="F116" s="1">
         <v>51</v>
       </c>
-      <c r="G116" s="4">
+      <c r="G116" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>10373</v>
       </c>
@@ -15680,11 +15691,11 @@
       <c r="F117" s="1">
         <v>89</v>
       </c>
-      <c r="G117" s="4">
+      <c r="G117" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>10374</v>
       </c>
@@ -15703,11 +15714,11 @@
       <c r="F118" s="1">
         <v>75</v>
       </c>
-      <c r="G118" s="4">
+      <c r="G118" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>10375</v>
       </c>
@@ -15726,11 +15737,11 @@
       <c r="F119" s="1">
         <v>109</v>
       </c>
-      <c r="G119" s="4">
+      <c r="G119" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>10376</v>
       </c>
@@ -15749,11 +15760,11 @@
       <c r="F120" s="1">
         <v>97</v>
       </c>
-      <c r="G120" s="4">
+      <c r="G120" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>10377</v>
       </c>
@@ -15772,11 +15783,11 @@
       <c r="F121" s="1">
         <v>52</v>
       </c>
-      <c r="G121" s="4">
+      <c r="G121" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>10378</v>
       </c>
@@ -15795,11 +15806,11 @@
       <c r="F122" s="1">
         <v>67</v>
       </c>
-      <c r="G122" s="4">
+      <c r="G122" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>10379</v>
       </c>
@@ -15818,11 +15829,11 @@
       <c r="F123" s="1">
         <v>91</v>
       </c>
-      <c r="G123" s="4">
+      <c r="G123" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>10380</v>
       </c>
@@ -15841,11 +15852,11 @@
       <c r="F124" s="1">
         <v>70</v>
       </c>
-      <c r="G124" s="4">
+      <c r="G124" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>10381</v>
       </c>
@@ -15864,11 +15875,11 @@
       <c r="F125" s="1">
         <v>73</v>
       </c>
-      <c r="G125" s="4">
+      <c r="G125" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>10382</v>
       </c>
@@ -15887,11 +15898,11 @@
       <c r="F126" s="1">
         <v>110</v>
       </c>
-      <c r="G126" s="4">
+      <c r="G126" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>10383</v>
       </c>
@@ -15910,11 +15921,11 @@
       <c r="F127" s="1">
         <v>109</v>
       </c>
-      <c r="G127" s="4">
+      <c r="G127" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>10384</v>
       </c>
@@ -15933,11 +15944,11 @@
       <c r="F128" s="1">
         <v>92</v>
       </c>
-      <c r="G128" s="4">
+      <c r="G128" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>10385</v>
       </c>
@@ -15956,11 +15967,11 @@
       <c r="F129" s="1">
         <v>50</v>
       </c>
-      <c r="G129" s="4">
+      <c r="G129" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>10386</v>
       </c>
@@ -15979,11 +15990,11 @@
       <c r="F130" s="1">
         <v>59</v>
       </c>
-      <c r="G130" s="4">
+      <c r="G130" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>10387</v>
       </c>
@@ -16002,11 +16013,11 @@
       <c r="F131" s="1">
         <v>55</v>
       </c>
-      <c r="G131" s="4">
+      <c r="G131" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>10388</v>
       </c>
@@ -16025,11 +16036,11 @@
       <c r="F132" s="1">
         <v>94</v>
       </c>
-      <c r="G132" s="4">
+      <c r="G132" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>10389</v>
       </c>
@@ -16048,11 +16059,11 @@
       <c r="F133" s="1">
         <v>61</v>
       </c>
-      <c r="G133" s="4">
+      <c r="G133" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>10390</v>
       </c>
@@ -16071,11 +16082,11 @@
       <c r="F134" s="1">
         <v>92</v>
       </c>
-      <c r="G134" s="4">
+      <c r="G134" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>10391</v>
       </c>
@@ -16094,11 +16105,11 @@
       <c r="F135" s="1">
         <v>120</v>
       </c>
-      <c r="G135" s="4">
+      <c r="G135" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>10392</v>
       </c>
@@ -16117,11 +16128,11 @@
       <c r="F136" s="1">
         <v>80</v>
       </c>
-      <c r="G136" s="4">
+      <c r="G136" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>10393</v>
       </c>
@@ -16140,11 +16151,11 @@
       <c r="F137" s="1">
         <v>74</v>
       </c>
-      <c r="G137" s="4">
+      <c r="G137" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>10394</v>
       </c>
@@ -16163,11 +16174,11 @@
       <c r="F138" s="1">
         <v>81</v>
       </c>
-      <c r="G138" s="4">
+      <c r="G138" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>10395</v>
       </c>
@@ -16186,11 +16197,11 @@
       <c r="F139" s="1">
         <v>73</v>
       </c>
-      <c r="G139" s="4">
+      <c r="G139" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>10396</v>
       </c>
@@ -16209,11 +16220,11 @@
       <c r="F140" s="1">
         <v>115</v>
       </c>
-      <c r="G140" s="4">
+      <c r="G140" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>10397</v>
       </c>
@@ -16232,11 +16243,11 @@
       <c r="F141" s="1">
         <v>112</v>
       </c>
-      <c r="G141" s="4">
+      <c r="G141" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>10398</v>
       </c>
@@ -16255,11 +16266,11 @@
       <c r="F142" s="1">
         <v>75</v>
       </c>
-      <c r="G142" s="4">
+      <c r="G142" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>10399</v>
       </c>
@@ -16278,11 +16289,11 @@
       <c r="F143" s="1">
         <v>87</v>
       </c>
-      <c r="G143" s="4">
+      <c r="G143" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>10400</v>
       </c>
@@ -16301,11 +16312,11 @@
       <c r="F144" s="1">
         <v>50</v>
       </c>
-      <c r="G144" s="4">
+      <c r="G144" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>10401</v>
       </c>
@@ -16324,11 +16335,11 @@
       <c r="F145" s="1">
         <v>55</v>
       </c>
-      <c r="G145" s="4">
+      <c r="G145" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>10402</v>
       </c>
@@ -16347,11 +16358,11 @@
       <c r="F146" s="1">
         <v>65</v>
       </c>
-      <c r="G146" s="4">
+      <c r="G146" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>10403</v>
       </c>
@@ -16370,11 +16381,11 @@
       <c r="F147" s="1">
         <v>117</v>
       </c>
-      <c r="G147" s="4">
+      <c r="G147" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>10404</v>
       </c>
@@ -16393,11 +16404,11 @@
       <c r="F148" s="1">
         <v>100</v>
       </c>
-      <c r="G148" s="4">
+      <c r="G148" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>10405</v>
       </c>
@@ -16416,11 +16427,11 @@
       <c r="F149" s="1">
         <v>68</v>
       </c>
-      <c r="G149" s="4">
+      <c r="G149" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>10406</v>
       </c>
@@ -16439,11 +16450,11 @@
       <c r="F150" s="1">
         <v>86</v>
       </c>
-      <c r="G150" s="4">
+      <c r="G150" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>10407</v>
       </c>
@@ -16462,11 +16473,11 @@
       <c r="F151" s="1">
         <v>67</v>
       </c>
-      <c r="G151" s="4">
+      <c r="G151" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>10408</v>
       </c>
@@ -16485,11 +16496,11 @@
       <c r="F152" s="1">
         <v>80</v>
       </c>
-      <c r="G152" s="4">
+      <c r="G152" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>10409</v>
       </c>
@@ -16508,11 +16519,11 @@
       <c r="F153" s="1">
         <v>53</v>
       </c>
-      <c r="G153" s="4">
+      <c r="G153" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>10410</v>
       </c>
@@ -16531,11 +16542,11 @@
       <c r="F154" s="1">
         <v>120</v>
       </c>
-      <c r="G154" s="4">
+      <c r="G154" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>10411</v>
       </c>
@@ -16554,11 +16565,11 @@
       <c r="F155" s="1">
         <v>59</v>
       </c>
-      <c r="G155" s="4">
+      <c r="G155" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>10412</v>
       </c>
@@ -16577,11 +16588,11 @@
       <c r="F156" s="1">
         <v>85</v>
       </c>
-      <c r="G156" s="4">
+      <c r="G156" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>10413</v>
       </c>
@@ -16600,11 +16611,11 @@
       <c r="F157" s="1">
         <v>60</v>
       </c>
-      <c r="G157" s="4">
+      <c r="G157" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>10414</v>
       </c>
@@ -16623,11 +16634,11 @@
       <c r="F158" s="1">
         <v>72</v>
       </c>
-      <c r="G158" s="4">
+      <c r="G158" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>10415</v>
       </c>
@@ -16646,11 +16657,11 @@
       <c r="F159" s="1">
         <v>63</v>
       </c>
-      <c r="G159" s="4">
+      <c r="G159" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>10416</v>
       </c>
@@ -16669,11 +16680,11 @@
       <c r="F160" s="1">
         <v>75</v>
       </c>
-      <c r="G160" s="4">
+      <c r="G160" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>10417</v>
       </c>
@@ -16692,11 +16703,11 @@
       <c r="F161" s="1">
         <v>53</v>
       </c>
-      <c r="G161" s="4">
+      <c r="G161" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>10418</v>
       </c>
@@ -16715,11 +16726,11 @@
       <c r="F162" s="1">
         <v>107</v>
       </c>
-      <c r="G162" s="4">
+      <c r="G162" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>10419</v>
       </c>
@@ -16738,11 +16749,11 @@
       <c r="F163" s="1">
         <v>80</v>
       </c>
-      <c r="G163" s="4">
+      <c r="G163" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>10420</v>
       </c>
@@ -16761,11 +16772,11 @@
       <c r="F164" s="1">
         <v>69</v>
       </c>
-      <c r="G164" s="4">
+      <c r="G164" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>10421</v>
       </c>
@@ -16784,11 +16795,11 @@
       <c r="F165" s="1">
         <v>58</v>
       </c>
-      <c r="G165" s="4">
+      <c r="G165" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>10422</v>
       </c>
@@ -16807,11 +16818,11 @@
       <c r="F166" s="1">
         <v>60</v>
       </c>
-      <c r="G166" s="4">
+      <c r="G166" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>10423</v>
       </c>
@@ -16830,11 +16841,11 @@
       <c r="F167" s="1">
         <v>59</v>
       </c>
-      <c r="G167" s="4">
+      <c r="G167" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>10424</v>
       </c>
@@ -16853,11 +16864,11 @@
       <c r="F168" s="1">
         <v>77</v>
       </c>
-      <c r="G168" s="4">
+      <c r="G168" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>10425</v>
       </c>
@@ -16876,11 +16887,11 @@
       <c r="F169" s="1">
         <v>93</v>
       </c>
-      <c r="G169" s="4">
+      <c r="G169" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>10426</v>
       </c>
@@ -16899,11 +16910,11 @@
       <c r="F170" s="1">
         <v>78</v>
       </c>
-      <c r="G170" s="4">
+      <c r="G170" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>10427</v>
       </c>
@@ -16922,11 +16933,11 @@
       <c r="F171" s="1">
         <v>51</v>
       </c>
-      <c r="G171" s="4">
+      <c r="G171" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>10428</v>
       </c>
@@ -16945,11 +16956,11 @@
       <c r="F172" s="1">
         <v>89</v>
       </c>
-      <c r="G172" s="4">
+      <c r="G172" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>10429</v>
       </c>
@@ -16968,11 +16979,11 @@
       <c r="F173" s="1">
         <v>77</v>
       </c>
-      <c r="G173" s="4">
+      <c r="G173" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>10430</v>
       </c>
@@ -16991,11 +17002,11 @@
       <c r="F174" s="1">
         <v>86</v>
       </c>
-      <c r="G174" s="4">
+      <c r="G174" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>10431</v>
       </c>
@@ -17014,11 +17025,11 @@
       <c r="F175" s="1">
         <v>75</v>
       </c>
-      <c r="G175" s="4">
+      <c r="G175" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>10432</v>
       </c>
@@ -17037,11 +17048,11 @@
       <c r="F176" s="1">
         <v>88</v>
       </c>
-      <c r="G176" s="4">
+      <c r="G176" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>10433</v>
       </c>
@@ -17060,11 +17071,11 @@
       <c r="F177" s="1">
         <v>63</v>
       </c>
-      <c r="G177" s="4">
+      <c r="G177" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>10434</v>
       </c>
@@ -17083,11 +17094,11 @@
       <c r="F178" s="1">
         <v>103</v>
       </c>
-      <c r="G178" s="4">
+      <c r="G178" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>10435</v>
       </c>
@@ -17106,11 +17117,11 @@
       <c r="F179" s="1">
         <v>93</v>
       </c>
-      <c r="G179" s="4">
+      <c r="G179" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>10436</v>
       </c>
@@ -17129,11 +17140,11 @@
       <c r="F180" s="1">
         <v>108</v>
       </c>
-      <c r="G180" s="4">
+      <c r="G180" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>10437</v>
       </c>
@@ -17152,11 +17163,11 @@
       <c r="F181" s="1">
         <v>60</v>
       </c>
-      <c r="G181" s="4">
+      <c r="G181" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>10438</v>
       </c>
@@ -17175,11 +17186,11 @@
       <c r="F182" s="1">
         <v>68</v>
       </c>
-      <c r="G182" s="4">
+      <c r="G182" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>10439</v>
       </c>
@@ -17198,11 +17209,11 @@
       <c r="F183" s="1">
         <v>93</v>
       </c>
-      <c r="G183" s="4">
+      <c r="G183" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>10440</v>
       </c>
@@ -17221,11 +17232,11 @@
       <c r="F184" s="1">
         <v>63</v>
       </c>
-      <c r="G184" s="4">
+      <c r="G184" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>10441</v>
       </c>
@@ -17244,11 +17255,11 @@
       <c r="F185" s="1">
         <v>115</v>
       </c>
-      <c r="G185" s="4">
+      <c r="G185" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>10442</v>
       </c>
@@ -17267,11 +17278,11 @@
       <c r="F186" s="1">
         <v>71</v>
       </c>
-      <c r="G186" s="4">
+      <c r="G186" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>10443</v>
       </c>
@@ -17290,11 +17301,11 @@
       <c r="F187" s="1">
         <v>58</v>
       </c>
-      <c r="G187" s="4">
+      <c r="G187" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>10444</v>
       </c>
@@ -17313,11 +17324,11 @@
       <c r="F188" s="1">
         <v>105</v>
       </c>
-      <c r="G188" s="4">
+      <c r="G188" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>10445</v>
       </c>
@@ -17336,11 +17347,11 @@
       <c r="F189" s="1">
         <v>82</v>
       </c>
-      <c r="G189" s="4">
+      <c r="G189" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>10446</v>
       </c>
@@ -17359,11 +17370,11 @@
       <c r="F190" s="1">
         <v>80</v>
       </c>
-      <c r="G190" s="4">
+      <c r="G190" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>10447</v>
       </c>
@@ -17382,11 +17393,11 @@
       <c r="F191" s="1">
         <v>54</v>
       </c>
-      <c r="G191" s="4">
+      <c r="G191" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>10448</v>
       </c>
@@ -17405,11 +17416,11 @@
       <c r="F192" s="1">
         <v>85</v>
       </c>
-      <c r="G192" s="4">
+      <c r="G192" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>10449</v>
       </c>
@@ -17428,11 +17439,11 @@
       <c r="F193" s="1">
         <v>69</v>
       </c>
-      <c r="G193" s="4">
+      <c r="G193" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>10450</v>
       </c>
@@ -17451,11 +17462,11 @@
       <c r="F194" s="1">
         <v>108</v>
       </c>
-      <c r="G194" s="4">
+      <c r="G194" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>10451</v>
       </c>
@@ -17474,11 +17485,11 @@
       <c r="F195" s="1">
         <v>86</v>
       </c>
-      <c r="G195" s="4">
+      <c r="G195" s="3">
         <v>0.25</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>10452</v>
       </c>
@@ -17497,11 +17508,11 @@
       <c r="F196" s="1">
         <v>72</v>
       </c>
-      <c r="G196" s="4">
+      <c r="G196" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>10453</v>
       </c>
@@ -17520,11 +17531,11 @@
       <c r="F197" s="1">
         <v>52</v>
       </c>
-      <c r="G197" s="4">
+      <c r="G197" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>10454</v>
       </c>
@@ -17543,11 +17554,11 @@
       <c r="F198" s="1">
         <v>116</v>
       </c>
-      <c r="G198" s="4">
+      <c r="G198" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>10455</v>
       </c>
@@ -17566,7 +17577,7 @@
       <c r="F199" s="1">
         <v>78</v>
       </c>
-      <c r="G199" s="4">
+      <c r="G199" s="3">
         <v>0.15</v>
       </c>
     </row>
@@ -17575,14 +17586,14 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G199">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>0.05</formula>
       <formula>0.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>0.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17600,23 +17611,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1CA09E-041A-43C6-9D28-BA6118324107}">
   <dimension ref="A1:C198"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -17626,2145 +17637,2145 @@
         <v>855</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>54</v>
       </c>
       <c r="C4" s="2">
         <v>15.11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>75</v>
       </c>
       <c r="C5" s="2">
         <v>25.22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>92</v>
       </c>
       <c r="C6" s="2">
         <v>7.36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>77</v>
       </c>
       <c r="C7" s="2">
         <v>9.16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>19.05</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>78</v>
       </c>
       <c r="C9" s="2">
         <v>10.46</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>60</v>
       </c>
       <c r="C10" s="2">
         <v>23.37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>120</v>
       </c>
       <c r="C11" s="2">
         <v>41.03</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>118</v>
       </c>
       <c r="C12" s="2">
         <v>34.83</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>69</v>
       </c>
       <c r="C13" s="2">
         <v>14.41</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>87</v>
       </c>
       <c r="C14" s="2">
         <v>17.38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>53</v>
       </c>
       <c r="C15" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>96</v>
       </c>
       <c r="C16" s="2">
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <v>63</v>
       </c>
       <c r="C17" s="2">
         <v>49.74</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <v>93</v>
       </c>
       <c r="C18" s="2">
         <v>22.35</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>97</v>
       </c>
       <c r="C19" s="2">
         <v>20.67</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <v>67</v>
       </c>
       <c r="C20" s="2">
         <v>6.25</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <v>93</v>
       </c>
       <c r="C21" s="2">
         <v>40.08</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22">
         <v>85</v>
       </c>
       <c r="C22" s="2">
         <v>46.74</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <v>76</v>
       </c>
       <c r="C23" s="2">
         <v>11.65</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24">
         <v>50</v>
       </c>
       <c r="C24" s="2">
         <v>6.91</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25">
         <v>108</v>
       </c>
       <c r="C25" s="2">
         <v>19.260000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="16" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26">
         <v>92</v>
       </c>
       <c r="C26" s="2">
         <v>30.33</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27">
         <v>109</v>
       </c>
       <c r="C27" s="2">
         <v>35.99</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28">
         <v>65</v>
       </c>
       <c r="C28" s="2">
         <v>3.2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="16" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29">
         <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>16.29</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30">
         <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>27.42</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31">
         <v>112</v>
       </c>
       <c r="C31" s="2">
         <v>9.06</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32">
         <v>82</v>
       </c>
       <c r="C32" s="2">
         <v>27.35</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="16" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33">
         <v>109</v>
       </c>
       <c r="C33" s="2">
         <v>7.69</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34">
         <v>109</v>
       </c>
       <c r="C34" s="2">
         <v>18.260000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35">
         <v>59</v>
       </c>
       <c r="C35" s="2">
         <v>32.01</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36">
         <v>67</v>
       </c>
       <c r="C36" s="2">
         <v>28.03</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="16" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37">
         <v>98</v>
       </c>
       <c r="C37" s="2">
         <v>21.16</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="16" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38">
         <v>80</v>
       </c>
       <c r="C38" s="2">
         <v>7.49</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="16" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39">
         <v>115</v>
       </c>
       <c r="C39" s="2">
         <v>2.08</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="16" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40">
         <v>105</v>
       </c>
       <c r="C40" s="2">
         <v>8.0399999999999991</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41">
         <v>55</v>
       </c>
       <c r="C41" s="2">
         <v>48.86</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="16" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42">
         <v>86</v>
       </c>
       <c r="C42" s="2">
         <v>31.28</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="16" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43">
         <v>103</v>
       </c>
       <c r="C43" s="2">
         <v>29.96</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44">
         <v>115</v>
       </c>
       <c r="C44" s="2">
         <v>39.57</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="16" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45">
         <v>91</v>
       </c>
       <c r="C45" s="2">
         <v>11.77</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="16" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46">
         <v>73</v>
       </c>
       <c r="C46" s="2">
         <v>4.59</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="16" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47">
         <v>94</v>
       </c>
       <c r="C47" s="2">
         <v>42.03</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="16" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48">
         <v>109</v>
       </c>
       <c r="C48" s="2">
         <v>58.769999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="16" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49">
         <v>115</v>
       </c>
       <c r="C49" s="2">
         <v>49.57</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="16" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50">
         <v>120</v>
       </c>
       <c r="C50" s="2">
         <v>38.369999999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="16" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51">
         <v>65</v>
       </c>
       <c r="C51" s="2">
         <v>29.55</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="16" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52">
         <v>53</v>
       </c>
       <c r="C52" s="2">
         <v>14.45</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="16" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53">
         <v>63</v>
       </c>
       <c r="C53" s="2">
         <v>21.75</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="16" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54">
         <v>88</v>
       </c>
       <c r="C54" s="2">
         <v>15.57</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="16" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55">
         <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>22.81</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="16" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56">
         <v>111</v>
       </c>
       <c r="C56" s="2">
         <v>11.29</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="16" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57">
         <v>81</v>
       </c>
       <c r="C57" s="2">
         <v>13.64</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="16" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58">
         <v>86</v>
       </c>
       <c r="C58" s="2">
         <v>20.440000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="16" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59">
         <v>57</v>
       </c>
       <c r="C59" s="2">
         <v>48.21</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="16" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60">
         <v>103</v>
       </c>
       <c r="C60" s="2">
         <v>14.12</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="16" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61">
         <v>106</v>
       </c>
       <c r="C61" s="2">
         <v>3.42</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="16" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62">
         <v>111</v>
       </c>
       <c r="C62" s="2">
         <v>45.23</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="16" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63">
         <v>78</v>
       </c>
       <c r="C63" s="2">
         <v>33.97</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="16" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64">
         <v>62</v>
       </c>
       <c r="C64" s="2">
         <v>37.64</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="16" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65">
         <v>103</v>
       </c>
       <c r="C65" s="2">
         <v>35.17</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="16" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66">
         <v>55</v>
       </c>
       <c r="C66" s="2">
         <v>9.09</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="16" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67">
         <v>104</v>
       </c>
       <c r="C67" s="2">
         <v>46.18</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="16" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68">
         <v>100</v>
       </c>
       <c r="C68" s="2">
         <v>28.98</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="16" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69">
         <v>99</v>
       </c>
       <c r="C69" s="2">
         <v>18.88</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="16" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70">
         <v>66</v>
       </c>
       <c r="C70" s="2">
         <v>39.85</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="16" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71">
         <v>73</v>
       </c>
       <c r="C71" s="2">
         <v>46.57</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="16" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72">
         <v>85</v>
       </c>
       <c r="C72" s="2">
         <v>34.369999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="16" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73">
         <v>107</v>
       </c>
       <c r="C73" s="2">
         <v>20.37</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="16" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74">
         <v>92</v>
       </c>
       <c r="C74" s="2">
         <v>8.67</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="16" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75">
         <v>59</v>
       </c>
       <c r="C75" s="2">
         <v>44.96</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="16" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76">
         <v>120</v>
       </c>
       <c r="C76" s="2">
         <v>11.64</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="16" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77">
         <v>60</v>
       </c>
       <c r="C77" s="2">
         <v>30.42</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="16" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78">
         <v>85</v>
       </c>
       <c r="C78" s="2">
         <v>28.85</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="16" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79">
         <v>86</v>
       </c>
       <c r="C79" s="2">
         <v>43.62</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="16" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80">
         <v>53</v>
       </c>
       <c r="C80" s="2">
         <v>33.950000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="16" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81">
         <v>81</v>
       </c>
       <c r="C81" s="2">
         <v>4.54</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="16" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82">
         <v>113</v>
       </c>
       <c r="C82" s="2">
         <v>18.510000000000002</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="16" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83">
         <v>68</v>
       </c>
       <c r="C83" s="2">
         <v>37.020000000000003</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="16" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84">
         <v>116</v>
       </c>
       <c r="C84" s="2">
         <v>2.7</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="16" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85">
         <v>99</v>
       </c>
       <c r="C85" s="2">
         <v>43.25</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="16" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86">
         <v>93</v>
       </c>
       <c r="C86" s="2">
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="16" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87">
         <v>68</v>
       </c>
       <c r="C87" s="2">
         <v>46.45</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="16" t="s">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88">
         <v>120</v>
       </c>
       <c r="C88" s="2">
         <v>35.119999999999997</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="16" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89">
         <v>70</v>
       </c>
       <c r="C89" s="2">
         <v>28.24</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="16" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90">
         <v>71</v>
       </c>
       <c r="C90" s="2">
         <v>42.1</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="16" t="s">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B91">
         <v>117</v>
       </c>
       <c r="C91" s="2">
         <v>22.15</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="16" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="B92" s="3">
+      <c r="B92">
         <v>82</v>
       </c>
       <c r="C92" s="2">
         <v>33.03</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="16" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B93" s="3">
+      <c r="B93">
         <v>93</v>
       </c>
       <c r="C93" s="2">
         <v>31.19</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="16" t="s">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94">
         <v>64</v>
       </c>
       <c r="C94" s="2">
         <v>14.91</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="16" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B95" s="3">
+      <c r="B95">
         <v>103</v>
       </c>
       <c r="C95" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="16" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B96" s="3">
+      <c r="B96">
         <v>50</v>
       </c>
       <c r="C96" s="2">
         <v>33.46</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="16" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="B97" s="3">
+      <c r="B97">
         <v>63</v>
       </c>
       <c r="C97" s="2">
         <v>36.409999999999997</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="16" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B98">
         <v>108</v>
       </c>
       <c r="C98" s="2">
         <v>5.53</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="16" t="s">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99">
         <v>86</v>
       </c>
       <c r="C99" s="2">
         <v>29.16</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="16" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B100" s="3">
+      <c r="B100">
         <v>115</v>
       </c>
       <c r="C100" s="2">
         <v>38.909999999999997</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="16" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B101" s="3">
+      <c r="B101">
         <v>78</v>
       </c>
       <c r="C101" s="2">
         <v>35.56</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="16" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B102" s="3">
+      <c r="B102">
         <v>99</v>
       </c>
       <c r="C102" s="2">
         <v>18.489999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="16" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103">
         <v>111</v>
       </c>
       <c r="C103" s="2">
         <v>47.55</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="16" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B104" s="3">
+      <c r="B104">
         <v>94</v>
       </c>
       <c r="C104" s="2">
         <v>38.020000000000003</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="16" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="B105" s="3">
+      <c r="B105">
         <v>60</v>
       </c>
       <c r="C105" s="2">
         <v>39.1</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="16" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="B106" s="3">
+      <c r="B106">
         <v>89</v>
       </c>
       <c r="C106" s="2">
         <v>3.02</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="16" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B107">
         <v>105</v>
       </c>
       <c r="C107" s="2">
         <v>29.89</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="16" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="B108" s="3">
+      <c r="B108">
         <v>67</v>
       </c>
       <c r="C108" s="2">
         <v>46.18</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="16" t="s">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="B109" s="3">
+      <c r="B109">
         <v>90</v>
       </c>
       <c r="C109" s="2">
         <v>14.6</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="16" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B110" s="3">
+      <c r="B110">
         <v>66</v>
       </c>
       <c r="C110" s="2">
         <v>47.25</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="16" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="B111" s="3">
+      <c r="B111">
         <v>86</v>
       </c>
       <c r="C111" s="2">
         <v>7.72</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="16" t="s">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="B112" s="3">
+      <c r="B112">
         <v>76</v>
       </c>
       <c r="C112" s="2">
         <v>7.71</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="16" t="s">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113">
         <v>94</v>
       </c>
       <c r="C113" s="2">
         <v>8.84</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="16" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114">
         <v>55</v>
       </c>
       <c r="C114" s="2">
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="16" t="s">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115">
         <v>103</v>
       </c>
       <c r="C115" s="2">
         <v>45.54</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="16" t="s">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116">
         <v>71</v>
       </c>
       <c r="C116" s="2">
         <v>10.3</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="16" t="s">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117">
         <v>97</v>
       </c>
       <c r="C117" s="2">
         <v>24.58</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="16" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118">
         <v>68</v>
       </c>
       <c r="C118" s="2">
         <v>15.01</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="16" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119">
         <v>86</v>
       </c>
       <c r="C119" s="2">
         <v>47.41</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="16" t="s">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120">
         <v>63</v>
       </c>
       <c r="C120" s="2">
         <v>41.54</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="16" t="s">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121">
         <v>104</v>
       </c>
       <c r="C121" s="2">
         <v>23.79</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="16" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122">
         <v>50</v>
       </c>
       <c r="C122" s="2">
         <v>38.630000000000003</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="16" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123">
         <v>108</v>
       </c>
       <c r="C123" s="2">
         <v>46.13</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="16" t="s">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124">
         <v>106</v>
       </c>
       <c r="C124" s="2">
         <v>29.54</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="16" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B125" s="3">
+      <c r="B125">
         <v>56</v>
       </c>
       <c r="C125" s="2">
         <v>22.95</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="16" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B126" s="3">
+      <c r="B126">
         <v>60</v>
       </c>
       <c r="C126" s="2">
         <v>48.03</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="16" t="s">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="B127" s="3">
+      <c r="B127">
         <v>53</v>
       </c>
       <c r="C127" s="2">
         <v>42.13</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="16" t="s">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="B128" s="3">
+      <c r="B128">
         <v>80</v>
       </c>
       <c r="C128" s="2">
         <v>29.1</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="16" t="s">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B129" s="3">
+      <c r="B129">
         <v>83</v>
       </c>
       <c r="C129" s="2">
         <v>49.39</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="16" t="s">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B130" s="3">
+      <c r="B130">
         <v>68</v>
       </c>
       <c r="C130" s="2">
         <v>42.48</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="16" t="s">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B131">
         <v>111</v>
       </c>
       <c r="C131" s="2">
         <v>18.2</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="16" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132">
         <v>93</v>
       </c>
       <c r="C132" s="2">
         <v>47.35</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="16" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="B133" s="3">
+      <c r="B133">
         <v>80</v>
       </c>
       <c r="C133" s="2">
         <v>49.29</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="16" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B134" s="3">
+      <c r="B134">
         <v>117</v>
       </c>
       <c r="C134" s="2">
         <v>43.72</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="16" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B135" s="3">
+      <c r="B135">
         <v>92</v>
       </c>
       <c r="C135" s="2">
         <v>6.5</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="16" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="B136" s="3">
+      <c r="B136">
         <v>69</v>
       </c>
       <c r="C136" s="2">
         <v>16.04</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="16" t="s">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B137" s="3">
+      <c r="B137">
         <v>84</v>
       </c>
       <c r="C137" s="2">
         <v>19.010000000000002</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" s="16" t="s">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="B138" s="3">
+      <c r="B138">
         <v>63</v>
       </c>
       <c r="C138" s="2">
         <v>31.34</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="16" t="s">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139">
         <v>69</v>
       </c>
       <c r="C139" s="2">
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="16" t="s">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B140" s="3">
+      <c r="B140">
         <v>78</v>
       </c>
       <c r="C140" s="2">
         <v>4.08</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="16" t="s">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B141" s="3">
+      <c r="B141">
         <v>82</v>
       </c>
       <c r="C141" s="2">
         <v>34.44</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" s="16" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="B142" s="3">
+      <c r="B142">
         <v>93</v>
       </c>
       <c r="C142" s="2">
         <v>40.28</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" s="16" t="s">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B143" s="3">
+      <c r="B143">
         <v>108</v>
       </c>
       <c r="C143" s="2">
         <v>36.25</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" s="16" t="s">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="B144" s="3">
+      <c r="B144">
         <v>58</v>
       </c>
       <c r="C144" s="2">
         <v>18.29</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="16" t="s">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B145" s="3">
+      <c r="B145">
         <v>105</v>
       </c>
       <c r="C145" s="2">
         <v>9.42</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="16" t="s">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="B146" s="3">
+      <c r="B146">
         <v>52</v>
       </c>
       <c r="C146" s="2">
         <v>31.5</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="16" t="s">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="B147" s="3">
+      <c r="B147">
         <v>68</v>
       </c>
       <c r="C147" s="2">
         <v>28.01</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" s="16" t="s">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B148" s="3">
+      <c r="B148">
         <v>70</v>
       </c>
       <c r="C148" s="2">
         <v>9.64</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="16" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="B149" s="3">
+      <c r="B149">
         <v>75</v>
       </c>
       <c r="C149" s="2">
         <v>7.44</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="16" t="s">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B150" s="3">
+      <c r="B150">
         <v>98</v>
       </c>
       <c r="C150" s="2">
         <v>26.51</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="16" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="B151" s="3">
+      <c r="B151">
         <v>80</v>
       </c>
       <c r="C151" s="2">
         <v>6.11</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" s="16" t="s">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="B152" s="3">
+      <c r="B152">
         <v>54</v>
       </c>
       <c r="C152" s="2">
         <v>41.37</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" s="16" t="s">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="B153" s="3">
+      <c r="B153">
         <v>74</v>
       </c>
       <c r="C153" s="2">
         <v>23.04</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="16" t="s">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B154" s="3">
+      <c r="B154">
         <v>110</v>
       </c>
       <c r="C154" s="2">
         <v>19.739999999999998</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="16" t="s">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="B155" s="3">
+      <c r="B155">
         <v>77</v>
       </c>
       <c r="C155" s="2">
         <v>42.56</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" s="16" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B156" s="3">
+      <c r="B156">
         <v>82</v>
       </c>
       <c r="C156" s="2">
         <v>24.38</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" s="16" t="s">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B157" s="3">
+      <c r="B157">
         <v>67</v>
       </c>
       <c r="C157" s="2">
         <v>26.57</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" s="16" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="B158" s="3">
+      <c r="B158">
         <v>89</v>
       </c>
       <c r="C158" s="2">
         <v>17.95</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" s="16" t="s">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B159" s="3">
+      <c r="B159">
         <v>50</v>
       </c>
       <c r="C159" s="2">
         <v>12.1</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="16" t="s">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B160" s="3">
+      <c r="B160">
         <v>94</v>
       </c>
       <c r="C160" s="2">
         <v>18.43</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" s="16" t="s">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B161" s="3">
+      <c r="B161">
         <v>111</v>
       </c>
       <c r="C161" s="2">
         <v>41.15</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" s="16" t="s">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B162" s="3">
+      <c r="B162">
         <v>53</v>
       </c>
       <c r="C162" s="2">
         <v>37.24</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" s="16" t="s">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B163" s="3">
+      <c r="B163">
         <v>95</v>
       </c>
       <c r="C163" s="2">
         <v>41.56</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" s="16" t="s">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="B164" s="3">
+      <c r="B164">
         <v>72</v>
       </c>
       <c r="C164" s="2">
         <v>27.41</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="16" t="s">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="B165" s="3">
+      <c r="B165">
         <v>86</v>
       </c>
       <c r="C165" s="2">
         <v>27.68</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" s="16" t="s">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="B166" s="3">
+      <c r="B166">
         <v>89</v>
       </c>
       <c r="C166" s="2">
         <v>27.35</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" s="16" t="s">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B167" s="3">
+      <c r="B167">
         <v>78</v>
       </c>
       <c r="C167" s="2">
         <v>8.51</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" s="16" t="s">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B168" s="3">
+      <c r="B168">
         <v>97</v>
       </c>
       <c r="C168" s="2">
         <v>26.59</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" s="16" t="s">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B169" s="3">
+      <c r="B169">
         <v>86</v>
       </c>
       <c r="C169" s="2">
         <v>7.18</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170" s="16" t="s">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B170" s="3">
+      <c r="B170">
         <v>93</v>
       </c>
       <c r="C170" s="2">
         <v>10.56</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="16" t="s">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="B171" s="3">
+      <c r="B171">
         <v>55</v>
       </c>
       <c r="C171" s="2">
         <v>41.78</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="16" t="s">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B172" s="3">
+      <c r="B172">
         <v>61</v>
       </c>
       <c r="C172" s="2">
         <v>33.619999999999997</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" s="16" t="s">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="B173" s="3">
+      <c r="B173">
         <v>56</v>
       </c>
       <c r="C173" s="2">
         <v>30.39</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" s="16" t="s">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B174" s="3">
+      <c r="B174">
         <v>98</v>
       </c>
       <c r="C174" s="2">
         <v>31.96</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="16" t="s">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B175" s="3">
+      <c r="B175">
         <v>90</v>
       </c>
       <c r="C175" s="2">
         <v>26.05</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" s="16" t="s">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B176" s="3">
+      <c r="B176">
         <v>85</v>
       </c>
       <c r="C176" s="2">
         <v>10.65</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177" s="16" t="s">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="B177" s="3">
+      <c r="B177">
         <v>75</v>
       </c>
       <c r="C177" s="2">
         <v>23.76</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" s="16" t="s">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B178" s="3">
+      <c r="B178">
         <v>70</v>
       </c>
       <c r="C178" s="2">
         <v>41.81</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179" s="16" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B179" s="3">
+      <c r="B179">
         <v>103</v>
       </c>
       <c r="C179" s="2">
         <v>44.87</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180" s="16" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="B180" s="3">
+      <c r="B180">
         <v>51</v>
       </c>
       <c r="C180" s="2">
         <v>13.06</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" s="16" t="s">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="B181" s="3">
+      <c r="B181">
         <v>110</v>
       </c>
       <c r="C181" s="2">
         <v>3.63</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" s="16" t="s">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="B182" s="3">
+      <c r="B182">
         <v>73</v>
       </c>
       <c r="C182" s="2">
         <v>41.5</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183" s="16" t="s">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B183" s="3">
+      <c r="B183">
         <v>86</v>
       </c>
       <c r="C183" s="2">
         <v>22.78</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184" s="16" t="s">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B184" s="3">
+      <c r="B184">
         <v>115</v>
       </c>
       <c r="C184" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" s="16" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="B185" s="3">
+      <c r="B185">
         <v>107</v>
       </c>
       <c r="C185" s="2">
         <v>12.34</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A186" s="16" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B186" s="3">
+      <c r="B186">
         <v>117</v>
       </c>
       <c r="C186" s="2">
         <v>40.89</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187" s="16" t="s">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="B187" s="3">
+      <c r="B187">
         <v>63</v>
       </c>
       <c r="C187" s="2">
         <v>29.58</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="16" t="s">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="B188" s="3">
+      <c r="B188">
         <v>116</v>
       </c>
       <c r="C188" s="2">
         <v>45.83</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" s="16" t="s">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="B189" s="3">
+      <c r="B189">
         <v>97</v>
       </c>
       <c r="C189" s="2">
         <v>41.46</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" s="16" t="s">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="B190" s="3">
+      <c r="B190">
         <v>92</v>
       </c>
       <c r="C190" s="2">
         <v>49.38</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" s="16" t="s">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B191" s="3">
+      <c r="B191">
         <v>146</v>
       </c>
       <c r="C191" s="2">
         <v>30.959999999999997</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" s="16" t="s">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B192" s="3">
+      <c r="B192">
         <v>50</v>
       </c>
       <c r="C192" s="2">
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="16" t="s">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="B193" s="3">
+      <c r="B193">
         <v>75</v>
       </c>
       <c r="C193" s="2">
         <v>16.690000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" s="16" t="s">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B194" s="3">
+      <c r="B194">
         <v>55</v>
       </c>
       <c r="C194" s="2">
         <v>47.76</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="16" t="s">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="B195" s="3">
+      <c r="B195">
         <v>52</v>
       </c>
       <c r="C195" s="2">
         <v>22.02</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" s="16" t="s">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B196" s="3">
+      <c r="B196">
         <v>97</v>
       </c>
       <c r="C196" s="2">
         <v>3.15</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" s="16" t="s">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="B197" s="3">
+      <c r="B197">
         <v>115</v>
       </c>
       <c r="C197" s="2">
         <v>16.14</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" s="16" t="s">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="B198" s="3">
+      <c r="B198">
         <v>16440</v>
       </c>
       <c r="C198" s="2">
@@ -19780,31 +19791,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F312BD6-EFB7-4E4C-B126-C76CF4CB60B3}">
   <dimension ref="A1:E83"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" customWidth="1"/>
-    <col min="4" max="4" width="41.88671875" customWidth="1"/>
+    <col min="1" max="1" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row r="2" spans="1:5" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="6"/>
+      <c r="D2" s="5" t="s">
         <v>850</v>
       </c>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -19818,7 +19829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>778</v>
       </c>
@@ -19827,7 +19838,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>424</v>
       </c>
@@ -19836,7 +19847,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>779</v>
       </c>
@@ -19845,7 +19856,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>780</v>
       </c>
@@ -19854,7 +19865,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>781</v>
       </c>
@@ -19863,7 +19874,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>782</v>
       </c>
@@ -19872,7 +19883,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -19881,7 +19892,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>571</v>
       </c>
@@ -19890,7 +19901,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>426</v>
       </c>
@@ -19899,7 +19910,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>783</v>
       </c>
@@ -19908,7 +19919,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>784</v>
       </c>
@@ -19917,7 +19928,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>785</v>
       </c>
@@ -19926,7 +19937,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>420</v>
       </c>
@@ -19935,7 +19946,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -19944,7 +19955,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -19953,7 +19964,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>786</v>
       </c>
@@ -19962,7 +19973,7 @@
       </c>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>787</v>
       </c>
@@ -19971,7 +19982,7 @@
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>788</v>
       </c>
@@ -19980,7 +19991,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>789</v>
       </c>
@@ -19989,7 +20000,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>790</v>
       </c>
@@ -19998,7 +20009,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>791</v>
       </c>
@@ -20007,7 +20018,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>792</v>
       </c>
@@ -20016,7 +20027,7 @@
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>793</v>
       </c>
@@ -20025,7 +20036,7 @@
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>794</v>
       </c>
@@ -20034,7 +20045,7 @@
       </c>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>795</v>
       </c>
@@ -20043,7 +20054,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>796</v>
       </c>
@@ -20052,7 +20063,7 @@
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>797</v>
       </c>
@@ -20061,7 +20072,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>798</v>
       </c>
@@ -20070,7 +20081,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>799</v>
       </c>
@@ -20079,7 +20090,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>800</v>
       </c>
@@ -20088,7 +20099,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>801</v>
       </c>
@@ -20097,7 +20108,7 @@
       </c>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -20106,7 +20117,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>802</v>
       </c>
@@ -20115,7 +20126,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>803</v>
       </c>
@@ -20124,7 +20135,7 @@
       </c>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>804</v>
       </c>
@@ -20133,7 +20144,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>805</v>
       </c>
@@ -20142,7 +20153,7 @@
       </c>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>806</v>
       </c>
@@ -20151,7 +20162,7 @@
       </c>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>807</v>
       </c>
@@ -20160,7 +20171,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>808</v>
       </c>
@@ -20169,7 +20180,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>809</v>
       </c>
@@ -20178,7 +20189,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>810</v>
       </c>
@@ -20187,7 +20198,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>811</v>
       </c>
@@ -20196,7 +20207,7 @@
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>812</v>
       </c>
@@ -20205,7 +20216,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>813</v>
       </c>
@@ -20214,7 +20225,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>814</v>
       </c>
@@ -20223,7 +20234,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>815</v>
       </c>
@@ -20232,7 +20243,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>816</v>
       </c>
@@ -20241,7 +20252,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>817</v>
       </c>
@@ -20250,7 +20261,7 @@
       </c>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>818</v>
       </c>
@@ -20259,7 +20270,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>819</v>
       </c>
@@ -20268,7 +20279,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>820</v>
       </c>
@@ -20277,7 +20288,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>821</v>
       </c>
@@ -20286,7 +20297,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>822</v>
       </c>
@@ -20295,7 +20306,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>823</v>
       </c>
@@ -20304,7 +20315,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>824</v>
       </c>
@@ -20313,7 +20324,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>825</v>
       </c>
@@ -20322,7 +20333,7 @@
       </c>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>826</v>
       </c>
@@ -20331,7 +20342,7 @@
       </c>
       <c r="E60" s="2"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>827</v>
       </c>
@@ -20340,7 +20351,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>828</v>
       </c>
@@ -20349,7 +20360,7 @@
       </c>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>829</v>
       </c>
@@ -20358,7 +20369,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>830</v>
       </c>
@@ -20367,7 +20378,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>831</v>
       </c>
@@ -20376,7 +20387,7 @@
       </c>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>832</v>
       </c>
@@ -20385,7 +20396,7 @@
       </c>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>833</v>
       </c>
@@ -20394,7 +20405,7 @@
       </c>
       <c r="E67" s="2"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>834</v>
       </c>
@@ -20403,7 +20414,7 @@
       </c>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>835</v>
       </c>
@@ -20412,7 +20423,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>836</v>
       </c>
@@ -20421,7 +20432,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>837</v>
       </c>
@@ -20430,7 +20441,7 @@
       </c>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>838</v>
       </c>
@@ -20439,7 +20450,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>839</v>
       </c>
@@ -20448,7 +20459,7 @@
       </c>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>840</v>
       </c>
@@ -20457,7 +20468,7 @@
       </c>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>841</v>
       </c>
@@ -20466,7 +20477,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>842</v>
       </c>
@@ -20475,7 +20486,7 @@
       </c>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>843</v>
       </c>
@@ -20484,7 +20495,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>844</v>
       </c>
@@ -20493,7 +20504,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>845</v>
       </c>
@@ -20502,7 +20513,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>846</v>
       </c>
@@ -20511,7 +20522,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>847</v>
       </c>
@@ -20520,7 +20531,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>848</v>
       </c>
@@ -20529,7 +20540,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>849</v>
       </c>
@@ -20554,37 +20565,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EEF4ED-7251-4885-B149-E85D77E0FB39}">
   <dimension ref="A1:H80"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="8" max="8" width="40.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="H2" s="11" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="H2" s="10" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>414</v>
       </c>
@@ -20603,9 +20614,9 @@
       <c r="F3" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="H3" s="12"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H3" s="11"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>419</v>
       </c>
@@ -20623,7 +20634,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>421</v>
       </c>
@@ -20641,7 +20652,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>423</v>
       </c>
@@ -20659,7 +20670,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>425</v>
       </c>
@@ -20679,7 +20690,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>428</v>
       </c>
@@ -20699,7 +20710,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>429</v>
       </c>
@@ -20717,7 +20728,7 @@
       </c>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>431</v>
       </c>
@@ -20735,7 +20746,7 @@
       </c>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>433</v>
       </c>
@@ -20755,7 +20766,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>435</v>
       </c>
@@ -20773,7 +20784,7 @@
       </c>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>437</v>
       </c>
@@ -20791,7 +20802,7 @@
       </c>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>439</v>
       </c>
@@ -20809,7 +20820,7 @@
       </c>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>441</v>
       </c>
@@ -20827,7 +20838,7 @@
       </c>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>443</v>
       </c>
@@ -20845,7 +20856,7 @@
       </c>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>445</v>
       </c>
@@ -20863,7 +20874,7 @@
       </c>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>447</v>
       </c>
@@ -20881,7 +20892,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>449</v>
       </c>
@@ -20899,7 +20910,7 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>451</v>
       </c>
@@ -20919,7 +20930,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>453</v>
       </c>
@@ -20937,7 +20948,7 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>455</v>
       </c>
@@ -20955,7 +20966,7 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>457</v>
       </c>
@@ -20973,7 +20984,7 @@
       </c>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>459</v>
       </c>
@@ -20991,7 +21002,7 @@
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>461</v>
       </c>
@@ -21009,7 +21020,7 @@
       </c>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>463</v>
       </c>
@@ -21027,7 +21038,7 @@
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>465</v>
       </c>
@@ -21045,7 +21056,7 @@
       </c>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>467</v>
       </c>
@@ -21063,7 +21074,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>469</v>
       </c>
@@ -21081,7 +21092,7 @@
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>471</v>
       </c>
@@ -21099,7 +21110,7 @@
       </c>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>473</v>
       </c>
@@ -21117,7 +21128,7 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>475</v>
       </c>
@@ -21137,7 +21148,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>477</v>
       </c>
@@ -21155,7 +21166,7 @@
       </c>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>479</v>
       </c>
@@ -21173,7 +21184,7 @@
       </c>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>481</v>
       </c>
@@ -21191,7 +21202,7 @@
       </c>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>483</v>
       </c>
@@ -21209,7 +21220,7 @@
       </c>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>485</v>
       </c>
@@ -21227,7 +21238,7 @@
       </c>
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>487</v>
       </c>
@@ -21245,7 +21256,7 @@
       </c>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>489</v>
       </c>
@@ -21263,7 +21274,7 @@
       </c>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>491</v>
       </c>
@@ -21281,7 +21292,7 @@
       </c>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>493</v>
       </c>
@@ -21299,7 +21310,7 @@
       </c>
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>495</v>
       </c>
@@ -21317,7 +21328,7 @@
       </c>
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>497</v>
       </c>
@@ -21335,7 +21346,7 @@
       </c>
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>498</v>
       </c>
@@ -21353,7 +21364,7 @@
       </c>
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>500</v>
       </c>
@@ -21371,7 +21382,7 @@
       </c>
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>502</v>
       </c>
@@ -21389,7 +21400,7 @@
       </c>
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>504</v>
       </c>
@@ -21407,7 +21418,7 @@
       </c>
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>506</v>
       </c>
@@ -21425,7 +21436,7 @@
       </c>
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>508</v>
       </c>
@@ -21443,7 +21454,7 @@
       </c>
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>510</v>
       </c>
@@ -21461,7 +21472,7 @@
       </c>
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>512</v>
       </c>
@@ -21479,7 +21490,7 @@
       </c>
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>514</v>
       </c>
@@ -21497,7 +21508,7 @@
       </c>
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>516</v>
       </c>
@@ -21515,7 +21526,7 @@
       </c>
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>518</v>
       </c>
@@ -21533,7 +21544,7 @@
       </c>
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>520</v>
       </c>
@@ -21551,7 +21562,7 @@
       </c>
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>522</v>
       </c>
@@ -21571,7 +21582,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>524</v>
       </c>
@@ -21589,7 +21600,7 @@
       </c>
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>526</v>
       </c>
@@ -21607,7 +21618,7 @@
       </c>
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>528</v>
       </c>
@@ -21625,7 +21636,7 @@
       </c>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>530</v>
       </c>
@@ -21643,7 +21654,7 @@
       </c>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>532</v>
       </c>
@@ -21661,7 +21672,7 @@
       </c>
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>534</v>
       </c>
@@ -21679,7 +21690,7 @@
       </c>
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>536</v>
       </c>
@@ -21697,7 +21708,7 @@
       </c>
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>538</v>
       </c>
@@ -21715,7 +21726,7 @@
       </c>
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>540</v>
       </c>
@@ -21733,7 +21744,7 @@
       </c>
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>542</v>
       </c>
@@ -21751,7 +21762,7 @@
       </c>
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>544</v>
       </c>
@@ -21769,7 +21780,7 @@
       </c>
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>546</v>
       </c>
@@ -21787,7 +21798,7 @@
       </c>
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>548</v>
       </c>
@@ -21805,7 +21816,7 @@
       </c>
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>550</v>
       </c>
@@ -21823,7 +21834,7 @@
       </c>
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>552</v>
       </c>
@@ -21841,7 +21852,7 @@
       </c>
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>553</v>
       </c>
@@ -21859,7 +21870,7 @@
       </c>
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>555</v>
       </c>
@@ -21877,7 +21888,7 @@
       </c>
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>557</v>
       </c>
@@ -21897,7 +21908,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>559</v>
       </c>
@@ -21917,7 +21928,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>561</v>
       </c>
@@ -21935,7 +21946,7 @@
       </c>
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>563</v>
       </c>
@@ -21953,7 +21964,7 @@
       </c>
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>565</v>
       </c>
@@ -21971,7 +21982,7 @@
       </c>
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>567</v>
       </c>
@@ -21989,7 +22000,7 @@
       </c>
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>570</v>
       </c>

--- a/data/key1/proyect5/files/Wide World Importers.xlsx
+++ b/data/key1/proyect5/files/Wide World Importers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Teacher Sergio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43402D9-9188-489C-9F6B-AD0F77901B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5FFD1F-6C61-4FF0-9754-9D421F8331CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="20700" windowHeight="7410" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="945" windowWidth="20490" windowHeight="9855" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="766">
   <si>
     <t>Order ID</t>
   </si>
@@ -1758,9 +1758,6 @@
     <t>Bratwurst</t>
   </si>
   <si>
-    <t>CS877</t>
-  </si>
-  <si>
     <t>Adventure Works Cycles</t>
   </si>
   <si>
@@ -1773,9 +1770,6 @@
     <t>Germany</t>
   </si>
   <si>
-    <t>CS810</t>
-  </si>
-  <si>
     <t>Fourth Coffee</t>
   </si>
   <si>
@@ -1788,18 +1782,12 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>CS814</t>
-  </si>
-  <si>
     <t>Contoso Ltd.</t>
   </si>
   <si>
     <t>Abbas Syed</t>
   </si>
   <si>
-    <t>CS894</t>
-  </si>
-  <si>
     <t>Bellows College</t>
   </si>
   <si>
@@ -1809,9 +1797,6 @@
     <t>United Kingdom</t>
   </si>
   <si>
-    <t>CS827</t>
-  </si>
-  <si>
     <t>Abolrous Hazem</t>
   </si>
   <si>
@@ -1821,18 +1806,12 @@
     <t>Sweden</t>
   </si>
   <si>
-    <t>CS893</t>
-  </si>
-  <si>
     <t>Contoso Pharmaceuticals</t>
   </si>
   <si>
     <t>Kern Sutton</t>
   </si>
   <si>
-    <t>CS820</t>
-  </si>
-  <si>
     <t>Contoso Suites</t>
   </si>
   <si>
@@ -1845,9 +1824,6 @@
     <t>France</t>
   </si>
   <si>
-    <t>CS866</t>
-  </si>
-  <si>
     <t>Fabrikam Residences</t>
   </si>
   <si>
@@ -1857,499 +1833,250 @@
     <t>Spain</t>
   </si>
   <si>
-    <t>CS801</t>
-  </si>
-  <si>
     <t>Smith John</t>
   </si>
   <si>
-    <t>CS802</t>
-  </si>
-  <si>
     <t>Garcia Maria</t>
   </si>
   <si>
-    <t>CS803</t>
-  </si>
-  <si>
     <t>Chen Wei</t>
   </si>
   <si>
-    <t>CS804</t>
-  </si>
-  <si>
     <t>Patel Raj</t>
   </si>
   <si>
-    <t>CS805</t>
-  </si>
-  <si>
     <t>Andersson Lars</t>
   </si>
   <si>
-    <t>CS806</t>
-  </si>
-  <si>
     <t>Müller Anna</t>
   </si>
   <si>
-    <t>CS807</t>
-  </si>
-  <si>
     <t>Dubois Pierre</t>
   </si>
   <si>
-    <t>CS808</t>
-  </si>
-  <si>
     <t>Rodriguez Carlos</t>
   </si>
   <si>
-    <t>CS809</t>
-  </si>
-  <si>
     <t>Schmidt Klaus</t>
   </si>
   <si>
-    <t>CS811</t>
-  </si>
-  <si>
     <t>Hernandez Luis</t>
   </si>
   <si>
-    <t>CS812</t>
-  </si>
-  <si>
     <t>Wong David</t>
   </si>
   <si>
-    <t>CS813</t>
-  </si>
-  <si>
     <t>Brown Emily</t>
   </si>
   <si>
-    <t>CS815</t>
-  </si>
-  <si>
     <t>Johansson Erik</t>
   </si>
   <si>
-    <t>CS816</t>
-  </si>
-  <si>
     <t>Schulz Thomas</t>
   </si>
   <si>
-    <t>CS817</t>
-  </si>
-  <si>
     <t>Martin Sophie</t>
   </si>
   <si>
-    <t>CS818</t>
-  </si>
-  <si>
     <t>Silva Fernando</t>
   </si>
   <si>
-    <t>CS819</t>
-  </si>
-  <si>
     <t>Fischer Hans</t>
   </si>
   <si>
-    <t>CS821</t>
-  </si>
-  <si>
     <t>Martinez Juan</t>
   </si>
   <si>
-    <t>CS822</t>
-  </si>
-  <si>
     <t>Kim Min</t>
   </si>
   <si>
-    <t>CS823</t>
-  </si>
-  <si>
     <t>Davis Sarah</t>
   </si>
   <si>
-    <t>CS824</t>
-  </si>
-  <si>
     <t>Nilsson Peter</t>
   </si>
   <si>
-    <t>CS825</t>
-  </si>
-  <si>
     <t>Weber Michael</t>
   </si>
   <si>
-    <t>CS826</t>
-  </si>
-  <si>
     <t>Bernard Claire</t>
   </si>
   <si>
-    <t>CS828</t>
-  </si>
-  <si>
     <t>Costa Antonio</t>
   </si>
   <si>
-    <t>CS829</t>
-  </si>
-  <si>
     <t>Becker Stefan</t>
   </si>
   <si>
-    <t>CS830</t>
-  </si>
-  <si>
     <t>Ramirez Carlos</t>
   </si>
   <si>
-    <t>CS831</t>
-  </si>
-  <si>
     <t>Tan James</t>
   </si>
   <si>
-    <t>CS832</t>
-  </si>
-  <si>
     <t>Wilson Emma</t>
   </si>
   <si>
-    <t>CS833</t>
-  </si>
-  <si>
     <t>Eriksson Anders</t>
   </si>
   <si>
-    <t>CS834</t>
-  </si>
-  <si>
     <t>Hoffmann Julia</t>
   </si>
   <si>
-    <t>CS835</t>
-  </si>
-  <si>
     <t>Moreau Luc</t>
   </si>
   <si>
-    <t>CS836</t>
-  </si>
-  <si>
     <t>Pereira Miguel</t>
   </si>
   <si>
-    <t>CS837</t>
-  </si>
-  <si>
     <t>Wagner Daniel</t>
   </si>
   <si>
-    <t>CS838</t>
-  </si>
-  <si>
     <t>Ortega Ana</t>
   </si>
   <si>
-    <t>CS839</t>
-  </si>
-  <si>
     <t>Nguyen Linh</t>
   </si>
   <si>
-    <t>CS840</t>
-  </si>
-  <si>
     <t>Taylor Olivia</t>
   </si>
   <si>
-    <t>CS841</t>
-  </si>
-  <si>
     <t>Larsson Johan</t>
   </si>
   <si>
-    <t>CS842</t>
-  </si>
-  <si>
     <t>Richter Sabine</t>
   </si>
   <si>
-    <t>CS843</t>
-  </si>
-  <si>
     <t>Petit Antoine</t>
   </si>
   <si>
-    <t>CS844</t>
-  </si>
-  <si>
     <t>Santos Paulo</t>
   </si>
   <si>
-    <t>CS845</t>
-  </si>
-  <si>
     <t>Huber Markus</t>
   </si>
   <si>
-    <t>CS846</t>
-  </si>
-  <si>
     <t>Flores Rosa</t>
   </si>
   <si>
-    <t>CS847</t>
-  </si>
-  <si>
     <t>Lee Soo</t>
   </si>
   <si>
-    <t>CS848</t>
-  </si>
-  <si>
     <t>Clark Noah</t>
   </si>
   <si>
-    <t>CS849</t>
-  </si>
-  <si>
     <t>Bergman Sofia</t>
   </si>
   <si>
-    <t>CS850</t>
-  </si>
-  <si>
     <t>Zimmermann Laura</t>
   </si>
   <si>
-    <t>CS851</t>
-  </si>
-  <si>
     <t>Girard Yves</t>
   </si>
   <si>
-    <t>CS852</t>
-  </si>
-  <si>
     <t>Ribeiro João</t>
   </si>
   <si>
-    <t>CS853</t>
-  </si>
-  <si>
     <t>Bauer Andreas</t>
   </si>
   <si>
-    <t>CS854</t>
-  </si>
-  <si>
     <t>Vargas Pedro</t>
   </si>
   <si>
-    <t>CS855</t>
-  </si>
-  <si>
     <t>Pham An</t>
   </si>
   <si>
-    <t>CS856</t>
-  </si>
-  <si>
     <t>Robinson Liam</t>
   </si>
   <si>
-    <t>CS857</t>
-  </si>
-  <si>
     <t>Svensson Maria</t>
   </si>
   <si>
-    <t>CS858</t>
-  </si>
-  <si>
     <t>Schneider Frank</t>
   </si>
   <si>
-    <t>CS859</t>
-  </si>
-  <si>
     <t>Lemoine Jean</t>
   </si>
   <si>
-    <t>CS860</t>
-  </si>
-  <si>
     <t>Almeida Tiago</t>
   </si>
   <si>
-    <t>CS861</t>
-  </si>
-  <si>
     <t>Koch Robert</t>
   </si>
   <si>
-    <t>CS862</t>
-  </si>
-  <si>
     <t>Castillo Diego</t>
   </si>
   <si>
-    <t>CS863</t>
-  </si>
-  <si>
     <t>Park Ji</t>
   </si>
   <si>
-    <t>CS864</t>
-  </si>
-  <si>
     <t>Walker Ava</t>
   </si>
   <si>
-    <t>CS865</t>
-  </si>
-  <si>
     <t>Nyström Lisa</t>
   </si>
   <si>
-    <t>CS867</t>
-  </si>
-  <si>
     <t>Hahn Simone</t>
   </si>
   <si>
-    <t>CS868</t>
-  </si>
-  <si>
     <t>Rousseau Marc</t>
   </si>
   <si>
-    <t>CS869</t>
-  </si>
-  <si>
     <t>Ferreira Luis</t>
   </si>
   <si>
-    <t>CS870</t>
-  </si>
-  <si>
     <t>Schröder Jens</t>
   </si>
   <si>
-    <t>CS871</t>
-  </si>
-  <si>
     <t>Mendez Lucia</t>
   </si>
   <si>
-    <t>CS872</t>
-  </si>
-  <si>
     <t>Tran Mai</t>
   </si>
   <si>
-    <t>CS873</t>
-  </si>
-  <si>
     <t>King Ethan</t>
   </si>
   <si>
-    <t>CS874</t>
-  </si>
-  <si>
     <t>Lindgren Karl</t>
   </si>
   <si>
-    <t>CS875</t>
-  </si>
-  <si>
     <t>Vogel Matthias</t>
   </si>
   <si>
-    <t>CS876</t>
-  </si>
-  <si>
     <t>Gauthier Marie</t>
   </si>
   <si>
-    <t>CS878</t>
-  </si>
-  <si>
     <t>Mendes Ricardo</t>
   </si>
   <si>
-    <t>CS879</t>
-  </si>
-  <si>
     <t>Frank Oliver</t>
   </si>
   <si>
-    <t>CS880</t>
-  </si>
-  <si>
     <t>Reyes Jorge</t>
   </si>
   <si>
-    <t>CS881</t>
-  </si>
-  <si>
     <t>Yamamoto Ken</t>
   </si>
   <si>
-    <t>CS882</t>
-  </si>
-  <si>
     <t>Scott Mia</t>
   </si>
   <si>
-    <t>CS883</t>
-  </si>
-  <si>
     <t>Pettersson Anna</t>
   </si>
   <si>
-    <t>CS884</t>
-  </si>
-  <si>
     <t>Berger Christina</t>
   </si>
   <si>
-    <t>CS885</t>
-  </si>
-  <si>
     <t>Blanc Philippe</t>
   </si>
   <si>
-    <t>CS886</t>
-  </si>
-  <si>
     <t>Cardoso Bruno</t>
   </si>
   <si>
-    <t>CS887</t>
-  </si>
-  <si>
     <t>Albrecht Timo</t>
   </si>
   <si>
-    <t>CS888</t>
-  </si>
-  <si>
     <t>Morales Sandra</t>
-  </si>
-  <si>
-    <t>CS889</t>
   </si>
   <si>
     <t>Singh Raj</t>
@@ -2759,7 +2486,13 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -10544,9 +10277,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A70C0944-03B6-4A5C-AC3E-4537E9BCC29E}" name="Table3" displayName="Table3" ref="A3:E94" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A70C0944-03B6-4A5C-AC3E-4537E9BCC29E}" name="Table3" displayName="Table3" ref="A3:E199" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B00E4194-227E-4F63-9388-FC3BC131E36D}" name="ID"/>
+    <tableColumn id="1" xr3:uid="{B00E4194-227E-4F63-9388-FC3BC131E36D}" name="ID" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{C909936A-DEB0-4A6A-A242-7D1CFEFCA42F}" name="Company Name"/>
     <tableColumn id="3" xr3:uid="{40031383-55A3-430D-BB08-7CE9E85FD3AA}" name="Customer Name"/>
     <tableColumn id="4" xr3:uid="{AA724D3A-9924-4ECB-BB12-C2A3740FFECB}" name="Contact Title"/>
@@ -10557,50 +10290,50 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OrdersTable" displayName="OrdersTable" ref="A3:H199" headerRowDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OrdersTable" displayName="OrdersTable" ref="A3:H199" headerRowDxfId="20">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Order ID" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order Date" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Customer ID" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Order ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order Date" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Customer ID" dataDxfId="17"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Product"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Unit Price" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Quantity" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Discount" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Region"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Unit Price" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Quantity" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Discount" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Region" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2B1A53F8-A39F-4C02-B164-EEA1F52574CE}" name="Table25" displayName="Table25" ref="A3:B83" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2B1A53F8-A39F-4C02-B164-EEA1F52574CE}" name="Table25" displayName="Table25" ref="A3:B83" totalsRowShown="0" headerRowDxfId="13">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{AF538A8F-098A-45C3-BFBD-B77A585C8F8B}" name="Product"/>
-    <tableColumn id="2" xr3:uid="{25F38738-0ABE-454D-B674-15131639985A}" name="Unit Price" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{25F38738-0ABE-454D-B674-15131639985A}" name="Unit Price" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EC7181DC-78EB-4F0D-A152-8E81FE2530D8}" name="Table257" displayName="Table257" ref="D3:E83" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EC7181DC-78EB-4F0D-A152-8E81FE2530D8}" name="Table257" displayName="Table257" ref="D3:E83" totalsRowShown="0" headerRowDxfId="11">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{ACF17F78-FD68-4AE4-B602-A29A8D8CFB59}" name="Product"/>
-    <tableColumn id="2" xr3:uid="{BAEA0B5B-3717-4873-A605-4231095D9965}" name="Unit Price" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{BAEA0B5B-3717-4873-A605-4231095D9965}" name="Unit Price" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41433919-C7EC-4C8C-A995-AE7259D9DBC0}" name="Table2" displayName="Table2" ref="A3:F80" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{41433919-C7EC-4C8C-A995-AE7259D9DBC0}" name="Table2" displayName="Table2" ref="A3:F80" totalsRowShown="0" headerRowDxfId="9">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{763562AD-1F50-4801-BE6D-6A57B2688737}" name="ID"/>
     <tableColumn id="2" xr3:uid="{D2643E02-B33E-4CF0-982F-0C0D4E3242BE}" name="Product Name"/>
-    <tableColumn id="3" xr3:uid="{BBC73D59-D513-4893-A1B1-8210CF4ACF5F}" name="Unit Price" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{C8934059-E678-40FC-BAF4-D911C1E803C2}" name="In Stock" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{629EE812-B522-490B-A09C-8C606E2E447B}" name="On Order" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{AFE626F5-90E0-4B8A-8E95-6F2F9A064DD1}" name="Discontinued" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{BBC73D59-D513-4893-A1B1-8210CF4ACF5F}" name="Unit Price" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{C8934059-E678-40FC-BAF4-D911C1E803C2}" name="In Stock" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{629EE812-B522-490B-A09C-8C606E2E447B}" name="On Order" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{AFE626F5-90E0-4B8A-8E95-6F2F9A064DD1}" name="Discontinued" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10891,7 +10624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD96B423-F0CF-48AC-BF42-DFD5442CB7E7}">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -10909,7 +10642,7 @@
     </row>
     <row r="2" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>774</v>
+        <v>683</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -10919,1563 +10652,2088 @@
         <v>414</v>
       </c>
       <c r="B3" t="s">
-        <v>771</v>
+        <v>680</v>
       </c>
       <c r="C3" t="s">
-        <v>772</v>
+        <v>681</v>
       </c>
       <c r="D3" t="s">
-        <v>773</v>
+        <v>682</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>572</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>573</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>574</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>575</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
         <v>577</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>578</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>579</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>580</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C6" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
+        <v>578</v>
+      </c>
+      <c r="E6" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
         <v>582</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
         <v>583</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D7" t="s">
+        <v>574</v>
+      </c>
+      <c r="E7" t="s">
         <v>584</v>
       </c>
-      <c r="D6" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>572</v>
+      </c>
+      <c r="C8" t="s">
+        <v>585</v>
+      </c>
+      <c r="D8" t="s">
+        <v>586</v>
+      </c>
+      <c r="E8" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>588</v>
+      </c>
+      <c r="C9" t="s">
+        <v>589</v>
+      </c>
+      <c r="D9" t="s">
+        <v>574</v>
+      </c>
+      <c r="E9" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>590</v>
+      </c>
+      <c r="C10" t="s">
+        <v>591</v>
+      </c>
+      <c r="D10" t="s">
+        <v>592</v>
+      </c>
+      <c r="E10" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>594</v>
+      </c>
+      <c r="C11" t="s">
+        <v>595</v>
+      </c>
+      <c r="D11" t="s">
+        <v>578</v>
+      </c>
+      <c r="E11" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>572</v>
+      </c>
+      <c r="C12" t="s">
+        <v>597</v>
+      </c>
+      <c r="D12" t="s">
+        <v>574</v>
+      </c>
+      <c r="E12" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>576</v>
+      </c>
+      <c r="C13" t="s">
+        <v>598</v>
+      </c>
+      <c r="D13" t="s">
+        <v>578</v>
+      </c>
+      <c r="E13" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
         <v>580</v>
       </c>
-      <c r="E6" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>585</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C14" t="s">
+        <v>599</v>
+      </c>
+      <c r="D14" t="s">
+        <v>578</v>
+      </c>
+      <c r="E14" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>582</v>
+      </c>
+      <c r="C15" t="s">
+        <v>600</v>
+      </c>
+      <c r="D15" t="s">
+        <v>574</v>
+      </c>
+      <c r="E15" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>572</v>
+      </c>
+      <c r="C16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D16" t="s">
         <v>586</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E16" t="s">
         <v>587</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>588</v>
+      </c>
+      <c r="C17" t="s">
+        <v>602</v>
+      </c>
+      <c r="D17" t="s">
+        <v>574</v>
+      </c>
+      <c r="E17" t="s">
         <v>575</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>590</v>
+      </c>
+      <c r="C18" t="s">
+        <v>603</v>
+      </c>
+      <c r="D18" t="s">
+        <v>592</v>
+      </c>
+      <c r="E18" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>594</v>
+      </c>
+      <c r="C19" t="s">
+        <v>604</v>
+      </c>
+      <c r="D19" t="s">
+        <v>578</v>
+      </c>
+      <c r="E19" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>572</v>
+      </c>
+      <c r="C20" t="s">
+        <v>605</v>
+      </c>
+      <c r="D20" t="s">
+        <v>574</v>
+      </c>
+      <c r="E20" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>576</v>
+      </c>
+      <c r="C21" t="s">
+        <v>606</v>
+      </c>
+      <c r="D21" t="s">
+        <v>578</v>
+      </c>
+      <c r="E21" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>580</v>
+      </c>
+      <c r="C22" t="s">
+        <v>607</v>
+      </c>
+      <c r="D22" t="s">
+        <v>578</v>
+      </c>
+      <c r="E22" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>582</v>
+      </c>
+      <c r="C23" t="s">
+        <v>608</v>
+      </c>
+      <c r="D23" t="s">
+        <v>574</v>
+      </c>
+      <c r="E23" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>572</v>
+      </c>
+      <c r="C24" t="s">
+        <v>609</v>
+      </c>
+      <c r="D24" t="s">
+        <v>586</v>
+      </c>
+      <c r="E24" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>589</v>
-      </c>
-      <c r="B8" t="s">
-        <v>573</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C25" t="s">
+        <v>610</v>
+      </c>
+      <c r="D25" t="s">
+        <v>574</v>
+      </c>
+      <c r="E25" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
         <v>590</v>
       </c>
-      <c r="D8" t="s">
-        <v>591</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="C26" t="s">
+        <v>611</v>
+      </c>
+      <c r="D26" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E26" t="s">
         <v>593</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" t="s">
         <v>594</v>
       </c>
-      <c r="C9" t="s">
-        <v>595</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C27" t="s">
+        <v>612</v>
+      </c>
+      <c r="D27" t="s">
+        <v>578</v>
+      </c>
+      <c r="E27" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" t="s">
+        <v>572</v>
+      </c>
+      <c r="C28" t="s">
+        <v>613</v>
+      </c>
+      <c r="D28" t="s">
+        <v>574</v>
+      </c>
+      <c r="E28" t="s">
         <v>575</v>
       </c>
-      <c r="E9" t="s">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C29" t="s">
+        <v>614</v>
+      </c>
+      <c r="D29" t="s">
+        <v>578</v>
+      </c>
+      <c r="E29" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>580</v>
+      </c>
+      <c r="C30" t="s">
+        <v>615</v>
+      </c>
+      <c r="D30" t="s">
+        <v>578</v>
+      </c>
+      <c r="E30" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
+        <v>582</v>
+      </c>
+      <c r="C31" t="s">
+        <v>616</v>
+      </c>
+      <c r="D31" t="s">
+        <v>574</v>
+      </c>
+      <c r="E31" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
+        <v>572</v>
+      </c>
+      <c r="C32" t="s">
+        <v>617</v>
+      </c>
+      <c r="D32" t="s">
+        <v>586</v>
+      </c>
+      <c r="E32" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>588</v>
+      </c>
+      <c r="C33" t="s">
+        <v>618</v>
+      </c>
+      <c r="D33" t="s">
+        <v>574</v>
+      </c>
+      <c r="E33" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>590</v>
+      </c>
+      <c r="C34" t="s">
+        <v>619</v>
+      </c>
+      <c r="D34" t="s">
+        <v>592</v>
+      </c>
+      <c r="E34" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
+        <v>594</v>
+      </c>
+      <c r="C35" t="s">
+        <v>620</v>
+      </c>
+      <c r="D35" t="s">
+        <v>578</v>
+      </c>
+      <c r="E35" t="s">
         <v>596</v>
       </c>
-      <c r="B10" t="s">
-        <v>597</v>
-      </c>
-      <c r="C10" t="s">
-        <v>598</v>
-      </c>
-      <c r="D10" t="s">
-        <v>599</v>
-      </c>
-      <c r="E10" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>601</v>
-      </c>
-      <c r="B11" t="s">
-        <v>602</v>
-      </c>
-      <c r="C11" t="s">
-        <v>603</v>
-      </c>
-      <c r="D11" t="s">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" t="s">
+        <v>572</v>
+      </c>
+      <c r="C36" t="s">
+        <v>621</v>
+      </c>
+      <c r="D36" t="s">
+        <v>574</v>
+      </c>
+      <c r="E36" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>576</v>
+      </c>
+      <c r="C37" t="s">
+        <v>622</v>
+      </c>
+      <c r="D37" t="s">
+        <v>578</v>
+      </c>
+      <c r="E37" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
         <v>580</v>
       </c>
-      <c r="E11" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>605</v>
-      </c>
-      <c r="B12" t="s">
-        <v>573</v>
-      </c>
-      <c r="C12" t="s">
-        <v>606</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C38" t="s">
+        <v>623</v>
+      </c>
+      <c r="D38" t="s">
+        <v>578</v>
+      </c>
+      <c r="E38" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s">
+        <v>582</v>
+      </c>
+      <c r="C39" t="s">
+        <v>624</v>
+      </c>
+      <c r="D39" t="s">
+        <v>574</v>
+      </c>
+      <c r="E39" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
+        <v>572</v>
+      </c>
+      <c r="C40" t="s">
+        <v>625</v>
+      </c>
+      <c r="D40" t="s">
+        <v>586</v>
+      </c>
+      <c r="E40" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
+        <v>588</v>
+      </c>
+      <c r="C41" t="s">
+        <v>626</v>
+      </c>
+      <c r="D41" t="s">
+        <v>574</v>
+      </c>
+      <c r="E41" t="s">
         <v>575</v>
       </c>
-      <c r="E12" t="s">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" t="s">
+        <v>590</v>
+      </c>
+      <c r="C42" t="s">
+        <v>627</v>
+      </c>
+      <c r="D42" t="s">
+        <v>592</v>
+      </c>
+      <c r="E42" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" t="s">
+        <v>594</v>
+      </c>
+      <c r="C43" t="s">
+        <v>628</v>
+      </c>
+      <c r="D43" t="s">
+        <v>578</v>
+      </c>
+      <c r="E43" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" t="s">
+        <v>572</v>
+      </c>
+      <c r="C44" t="s">
+        <v>629</v>
+      </c>
+      <c r="D44" t="s">
+        <v>574</v>
+      </c>
+      <c r="E44" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>607</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C45" t="s">
+        <v>630</v>
+      </c>
+      <c r="D45" t="s">
         <v>578</v>
       </c>
-      <c r="C13" t="s">
-        <v>608</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E45" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" t="s">
         <v>580</v>
       </c>
-      <c r="E13" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>609</v>
-      </c>
-      <c r="B14" t="s">
-        <v>583</v>
-      </c>
-      <c r="C14" t="s">
-        <v>610</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C46" t="s">
+        <v>631</v>
+      </c>
+      <c r="D46" t="s">
+        <v>578</v>
+      </c>
+      <c r="E46" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" t="s">
+        <v>582</v>
+      </c>
+      <c r="C47" t="s">
+        <v>632</v>
+      </c>
+      <c r="D47" t="s">
+        <v>574</v>
+      </c>
+      <c r="E47" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" t="s">
+        <v>572</v>
+      </c>
+      <c r="C48" t="s">
+        <v>633</v>
+      </c>
+      <c r="D48" t="s">
+        <v>586</v>
+      </c>
+      <c r="E48" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" t="s">
+        <v>588</v>
+      </c>
+      <c r="C49" t="s">
+        <v>634</v>
+      </c>
+      <c r="D49" t="s">
+        <v>574</v>
+      </c>
+      <c r="E49" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s">
+        <v>590</v>
+      </c>
+      <c r="C50" t="s">
+        <v>635</v>
+      </c>
+      <c r="D50" t="s">
+        <v>592</v>
+      </c>
+      <c r="E50" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" t="s">
+        <v>594</v>
+      </c>
+      <c r="C51" t="s">
+        <v>636</v>
+      </c>
+      <c r="D51" t="s">
+        <v>578</v>
+      </c>
+      <c r="E51" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" t="s">
+        <v>572</v>
+      </c>
+      <c r="C52" t="s">
+        <v>637</v>
+      </c>
+      <c r="D52" t="s">
+        <v>574</v>
+      </c>
+      <c r="E52" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" t="s">
+        <v>576</v>
+      </c>
+      <c r="C53" t="s">
+        <v>638</v>
+      </c>
+      <c r="D53" t="s">
+        <v>578</v>
+      </c>
+      <c r="E53" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" t="s">
         <v>580</v>
       </c>
-      <c r="E14" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>611</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C54" t="s">
+        <v>639</v>
+      </c>
+      <c r="D54" t="s">
+        <v>578</v>
+      </c>
+      <c r="E54" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" t="s">
+        <v>582</v>
+      </c>
+      <c r="C55" t="s">
+        <v>640</v>
+      </c>
+      <c r="D55" t="s">
+        <v>574</v>
+      </c>
+      <c r="E55" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" t="s">
+        <v>572</v>
+      </c>
+      <c r="C56" t="s">
+        <v>641</v>
+      </c>
+      <c r="D56" t="s">
         <v>586</v>
       </c>
-      <c r="C15" t="s">
-        <v>612</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E56" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" t="s">
+        <v>588</v>
+      </c>
+      <c r="C57" t="s">
+        <v>642</v>
+      </c>
+      <c r="D57" t="s">
+        <v>574</v>
+      </c>
+      <c r="E57" t="s">
         <v>575</v>
       </c>
-      <c r="E15" t="s">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B58" t="s">
+        <v>590</v>
+      </c>
+      <c r="C58" t="s">
+        <v>643</v>
+      </c>
+      <c r="D58" t="s">
+        <v>592</v>
+      </c>
+      <c r="E58" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" t="s">
+        <v>594</v>
+      </c>
+      <c r="C59" t="s">
+        <v>644</v>
+      </c>
+      <c r="D59" t="s">
+        <v>578</v>
+      </c>
+      <c r="E59" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" t="s">
+        <v>572</v>
+      </c>
+      <c r="C60" t="s">
+        <v>645</v>
+      </c>
+      <c r="D60" t="s">
+        <v>574</v>
+      </c>
+      <c r="E60" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" t="s">
+        <v>576</v>
+      </c>
+      <c r="C61" t="s">
+        <v>646</v>
+      </c>
+      <c r="D61" t="s">
+        <v>578</v>
+      </c>
+      <c r="E61" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" t="s">
+        <v>580</v>
+      </c>
+      <c r="C62" t="s">
+        <v>647</v>
+      </c>
+      <c r="D62" t="s">
+        <v>578</v>
+      </c>
+      <c r="E62" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" t="s">
+        <v>582</v>
+      </c>
+      <c r="C63" t="s">
+        <v>648</v>
+      </c>
+      <c r="D63" t="s">
+        <v>574</v>
+      </c>
+      <c r="E63" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" t="s">
+        <v>572</v>
+      </c>
+      <c r="C64" t="s">
+        <v>649</v>
+      </c>
+      <c r="D64" t="s">
+        <v>586</v>
+      </c>
+      <c r="E64" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>613</v>
-      </c>
-      <c r="B16" t="s">
-        <v>573</v>
-      </c>
-      <c r="C16" t="s">
-        <v>614</v>
-      </c>
-      <c r="D16" t="s">
-        <v>591</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="C65" t="s">
+        <v>650</v>
+      </c>
+      <c r="D65" t="s">
+        <v>574</v>
+      </c>
+      <c r="E65" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" t="s">
+        <v>590</v>
+      </c>
+      <c r="C66" t="s">
+        <v>651</v>
+      </c>
+      <c r="D66" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>615</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="E66" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" t="s">
         <v>594</v>
       </c>
-      <c r="C17" t="s">
-        <v>616</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C67" t="s">
+        <v>652</v>
+      </c>
+      <c r="D67" t="s">
+        <v>578</v>
+      </c>
+      <c r="E67" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B68" t="s">
+        <v>572</v>
+      </c>
+      <c r="C68" t="s">
+        <v>653</v>
+      </c>
+      <c r="D68" t="s">
+        <v>574</v>
+      </c>
+      <c r="E68" t="s">
         <v>575</v>
       </c>
-      <c r="E17" t="s">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>617</v>
-      </c>
-      <c r="B18" t="s">
-        <v>597</v>
-      </c>
-      <c r="C18" t="s">
-        <v>618</v>
-      </c>
-      <c r="D18" t="s">
-        <v>599</v>
-      </c>
-      <c r="E18" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>619</v>
-      </c>
-      <c r="B19" t="s">
-        <v>602</v>
-      </c>
-      <c r="C19" t="s">
-        <v>620</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C69" t="s">
+        <v>654</v>
+      </c>
+      <c r="D69" t="s">
+        <v>578</v>
+      </c>
+      <c r="E69" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" t="s">
         <v>580</v>
       </c>
-      <c r="E19" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>621</v>
-      </c>
-      <c r="B20" t="s">
-        <v>573</v>
-      </c>
-      <c r="C20" t="s">
-        <v>622</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C70" t="s">
+        <v>655</v>
+      </c>
+      <c r="D70" t="s">
+        <v>578</v>
+      </c>
+      <c r="E70" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B71" t="s">
+        <v>582</v>
+      </c>
+      <c r="C71" t="s">
+        <v>656</v>
+      </c>
+      <c r="D71" t="s">
+        <v>574</v>
+      </c>
+      <c r="E71" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" t="s">
+        <v>572</v>
+      </c>
+      <c r="C72" t="s">
+        <v>657</v>
+      </c>
+      <c r="D72" t="s">
+        <v>586</v>
+      </c>
+      <c r="E72" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B73" t="s">
+        <v>588</v>
+      </c>
+      <c r="C73" t="s">
+        <v>658</v>
+      </c>
+      <c r="D73" t="s">
+        <v>574</v>
+      </c>
+      <c r="E73" t="s">
         <v>575</v>
       </c>
-      <c r="E20" t="s">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B74" t="s">
+        <v>590</v>
+      </c>
+      <c r="C74" t="s">
+        <v>659</v>
+      </c>
+      <c r="D74" t="s">
+        <v>592</v>
+      </c>
+      <c r="E74" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B75" t="s">
+        <v>594</v>
+      </c>
+      <c r="C75" t="s">
+        <v>660</v>
+      </c>
+      <c r="D75" t="s">
+        <v>578</v>
+      </c>
+      <c r="E75" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" t="s">
+        <v>572</v>
+      </c>
+      <c r="C76" t="s">
+        <v>661</v>
+      </c>
+      <c r="D76" t="s">
+        <v>574</v>
+      </c>
+      <c r="E76" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B77" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>623</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C77" t="s">
+        <v>662</v>
+      </c>
+      <c r="D77" t="s">
         <v>578</v>
       </c>
-      <c r="C21" t="s">
-        <v>624</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E77" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B78" t="s">
         <v>580</v>
       </c>
-      <c r="E21" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>625</v>
-      </c>
-      <c r="B22" t="s">
-        <v>583</v>
-      </c>
-      <c r="C22" t="s">
-        <v>626</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C78" t="s">
+        <v>663</v>
+      </c>
+      <c r="D78" t="s">
+        <v>578</v>
+      </c>
+      <c r="E78" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B79" t="s">
+        <v>582</v>
+      </c>
+      <c r="C79" t="s">
+        <v>664</v>
+      </c>
+      <c r="D79" t="s">
+        <v>574</v>
+      </c>
+      <c r="E79" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B80" t="s">
+        <v>572</v>
+      </c>
+      <c r="C80" t="s">
+        <v>665</v>
+      </c>
+      <c r="D80" t="s">
+        <v>586</v>
+      </c>
+      <c r="E80" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" t="s">
+        <v>588</v>
+      </c>
+      <c r="C81" t="s">
+        <v>666</v>
+      </c>
+      <c r="D81" t="s">
+        <v>574</v>
+      </c>
+      <c r="E81" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B82" t="s">
+        <v>590</v>
+      </c>
+      <c r="C82" t="s">
+        <v>667</v>
+      </c>
+      <c r="D82" t="s">
+        <v>592</v>
+      </c>
+      <c r="E82" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B83" t="s">
+        <v>594</v>
+      </c>
+      <c r="C83" t="s">
+        <v>668</v>
+      </c>
+      <c r="D83" t="s">
+        <v>578</v>
+      </c>
+      <c r="E83" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B84" t="s">
+        <v>572</v>
+      </c>
+      <c r="C84" t="s">
+        <v>669</v>
+      </c>
+      <c r="D84" t="s">
+        <v>574</v>
+      </c>
+      <c r="E84" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B85" t="s">
+        <v>576</v>
+      </c>
+      <c r="C85" t="s">
+        <v>670</v>
+      </c>
+      <c r="D85" t="s">
+        <v>578</v>
+      </c>
+      <c r="E85" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B86" t="s">
         <v>580</v>
       </c>
-      <c r="E22" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>627</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C86" t="s">
+        <v>671</v>
+      </c>
+      <c r="D86" t="s">
+        <v>578</v>
+      </c>
+      <c r="E86" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B87" t="s">
+        <v>582</v>
+      </c>
+      <c r="C87" t="s">
+        <v>672</v>
+      </c>
+      <c r="D87" t="s">
+        <v>574</v>
+      </c>
+      <c r="E87" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B88" t="s">
+        <v>572</v>
+      </c>
+      <c r="C88" t="s">
+        <v>673</v>
+      </c>
+      <c r="D88" t="s">
         <v>586</v>
       </c>
-      <c r="C23" t="s">
-        <v>628</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E88" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B89" t="s">
+        <v>588</v>
+      </c>
+      <c r="C89" t="s">
+        <v>674</v>
+      </c>
+      <c r="D89" t="s">
+        <v>574</v>
+      </c>
+      <c r="E89" t="s">
         <v>575</v>
       </c>
-      <c r="E23" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>629</v>
-      </c>
-      <c r="B24" t="s">
-        <v>573</v>
-      </c>
-      <c r="C24" t="s">
-        <v>630</v>
-      </c>
-      <c r="D24" t="s">
-        <v>591</v>
-      </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B90" t="s">
+        <v>590</v>
+      </c>
+      <c r="C90" t="s">
+        <v>675</v>
+      </c>
+      <c r="D90" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>631</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="E90" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B91" t="s">
         <v>594</v>
       </c>
-      <c r="C25" t="s">
-        <v>632</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C91" t="s">
+        <v>676</v>
+      </c>
+      <c r="D91" t="s">
+        <v>578</v>
+      </c>
+      <c r="E91" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B92" t="s">
+        <v>572</v>
+      </c>
+      <c r="C92" t="s">
+        <v>677</v>
+      </c>
+      <c r="D92" t="s">
+        <v>574</v>
+      </c>
+      <c r="E92" t="s">
         <v>575</v>
       </c>
-      <c r="E25" t="s">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B93" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>633</v>
-      </c>
-      <c r="B26" t="s">
-        <v>597</v>
-      </c>
-      <c r="C26" t="s">
-        <v>634</v>
-      </c>
-      <c r="D26" t="s">
-        <v>599</v>
-      </c>
-      <c r="E26" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>635</v>
-      </c>
-      <c r="B27" t="s">
-        <v>602</v>
-      </c>
-      <c r="C27" t="s">
-        <v>636</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C93" t="s">
+        <v>678</v>
+      </c>
+      <c r="D93" t="s">
+        <v>578</v>
+      </c>
+      <c r="E93" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B94" t="s">
         <v>580</v>
       </c>
-      <c r="E27" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>637</v>
-      </c>
-      <c r="B28" t="s">
-        <v>573</v>
-      </c>
-      <c r="C28" t="s">
-        <v>638</v>
-      </c>
-      <c r="D28" t="s">
-        <v>575</v>
-      </c>
-      <c r="E28" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>639</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C94" t="s">
+        <v>679</v>
+      </c>
+      <c r="D94" t="s">
         <v>578</v>
       </c>
-      <c r="C29" t="s">
-        <v>640</v>
-      </c>
-      <c r="D29" t="s">
-        <v>580</v>
-      </c>
-      <c r="E29" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>641</v>
-      </c>
-      <c r="B30" t="s">
-        <v>583</v>
-      </c>
-      <c r="C30" t="s">
-        <v>642</v>
-      </c>
-      <c r="D30" t="s">
-        <v>580</v>
-      </c>
-      <c r="E30" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>643</v>
-      </c>
-      <c r="B31" t="s">
-        <v>586</v>
-      </c>
-      <c r="C31" t="s">
-        <v>644</v>
-      </c>
-      <c r="D31" t="s">
-        <v>575</v>
-      </c>
-      <c r="E31" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>645</v>
-      </c>
-      <c r="B32" t="s">
-        <v>573</v>
-      </c>
-      <c r="C32" t="s">
-        <v>646</v>
-      </c>
-      <c r="D32" t="s">
-        <v>591</v>
-      </c>
-      <c r="E32" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>647</v>
-      </c>
-      <c r="B33" t="s">
-        <v>594</v>
-      </c>
-      <c r="C33" t="s">
-        <v>648</v>
-      </c>
-      <c r="D33" t="s">
-        <v>575</v>
-      </c>
-      <c r="E33" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>649</v>
-      </c>
-      <c r="B34" t="s">
-        <v>597</v>
-      </c>
-      <c r="C34" t="s">
-        <v>650</v>
-      </c>
-      <c r="D34" t="s">
-        <v>599</v>
-      </c>
-      <c r="E34" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>651</v>
-      </c>
-      <c r="B35" t="s">
-        <v>602</v>
-      </c>
-      <c r="C35" t="s">
-        <v>652</v>
-      </c>
-      <c r="D35" t="s">
-        <v>580</v>
-      </c>
-      <c r="E35" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>653</v>
-      </c>
-      <c r="B36" t="s">
-        <v>573</v>
-      </c>
-      <c r="C36" t="s">
-        <v>654</v>
-      </c>
-      <c r="D36" t="s">
-        <v>575</v>
-      </c>
-      <c r="E36" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>655</v>
-      </c>
-      <c r="B37" t="s">
-        <v>578</v>
-      </c>
-      <c r="C37" t="s">
-        <v>656</v>
-      </c>
-      <c r="D37" t="s">
-        <v>580</v>
-      </c>
-      <c r="E37" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>657</v>
-      </c>
-      <c r="B38" t="s">
-        <v>583</v>
-      </c>
-      <c r="C38" t="s">
-        <v>658</v>
-      </c>
-      <c r="D38" t="s">
-        <v>580</v>
-      </c>
-      <c r="E38" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>659</v>
-      </c>
-      <c r="B39" t="s">
-        <v>586</v>
-      </c>
-      <c r="C39" t="s">
-        <v>660</v>
-      </c>
-      <c r="D39" t="s">
-        <v>575</v>
-      </c>
-      <c r="E39" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>661</v>
-      </c>
-      <c r="B40" t="s">
-        <v>573</v>
-      </c>
-      <c r="C40" t="s">
-        <v>662</v>
-      </c>
-      <c r="D40" t="s">
-        <v>591</v>
-      </c>
-      <c r="E40" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>663</v>
-      </c>
-      <c r="B41" t="s">
-        <v>594</v>
-      </c>
-      <c r="C41" t="s">
-        <v>664</v>
-      </c>
-      <c r="D41" t="s">
-        <v>575</v>
-      </c>
-      <c r="E41" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>665</v>
-      </c>
-      <c r="B42" t="s">
-        <v>597</v>
-      </c>
-      <c r="C42" t="s">
-        <v>666</v>
-      </c>
-      <c r="D42" t="s">
-        <v>599</v>
-      </c>
-      <c r="E42" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>667</v>
-      </c>
-      <c r="B43" t="s">
-        <v>602</v>
-      </c>
-      <c r="C43" t="s">
-        <v>668</v>
-      </c>
-      <c r="D43" t="s">
-        <v>580</v>
-      </c>
-      <c r="E43" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>669</v>
-      </c>
-      <c r="B44" t="s">
-        <v>573</v>
-      </c>
-      <c r="C44" t="s">
-        <v>670</v>
-      </c>
-      <c r="D44" t="s">
-        <v>575</v>
-      </c>
-      <c r="E44" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>671</v>
-      </c>
-      <c r="B45" t="s">
-        <v>578</v>
-      </c>
-      <c r="C45" t="s">
-        <v>672</v>
-      </c>
-      <c r="D45" t="s">
-        <v>580</v>
-      </c>
-      <c r="E45" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>673</v>
-      </c>
-      <c r="B46" t="s">
-        <v>583</v>
-      </c>
-      <c r="C46" t="s">
-        <v>674</v>
-      </c>
-      <c r="D46" t="s">
-        <v>580</v>
-      </c>
-      <c r="E46" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>675</v>
-      </c>
-      <c r="B47" t="s">
-        <v>586</v>
-      </c>
-      <c r="C47" t="s">
-        <v>676</v>
-      </c>
-      <c r="D47" t="s">
-        <v>575</v>
-      </c>
-      <c r="E47" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>677</v>
-      </c>
-      <c r="B48" t="s">
-        <v>573</v>
-      </c>
-      <c r="C48" t="s">
-        <v>678</v>
-      </c>
-      <c r="D48" t="s">
-        <v>591</v>
-      </c>
-      <c r="E48" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>679</v>
-      </c>
-      <c r="B49" t="s">
-        <v>594</v>
-      </c>
-      <c r="C49" t="s">
-        <v>680</v>
-      </c>
-      <c r="D49" t="s">
-        <v>575</v>
-      </c>
-      <c r="E49" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>681</v>
-      </c>
-      <c r="B50" t="s">
-        <v>597</v>
-      </c>
-      <c r="C50" t="s">
-        <v>682</v>
-      </c>
-      <c r="D50" t="s">
-        <v>599</v>
-      </c>
-      <c r="E50" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>683</v>
-      </c>
-      <c r="B51" t="s">
-        <v>602</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="E94" t="s">
         <v>684</v>
       </c>
-      <c r="D51" t="s">
-        <v>580</v>
-      </c>
-      <c r="E51" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>685</v>
-      </c>
-      <c r="B52" t="s">
-        <v>573</v>
-      </c>
-      <c r="C52" t="s">
-        <v>686</v>
-      </c>
-      <c r="D52" t="s">
-        <v>575</v>
-      </c>
-      <c r="E52" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>687</v>
-      </c>
-      <c r="B53" t="s">
-        <v>578</v>
-      </c>
-      <c r="C53" t="s">
-        <v>688</v>
-      </c>
-      <c r="D53" t="s">
-        <v>580</v>
-      </c>
-      <c r="E53" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>689</v>
-      </c>
-      <c r="B54" t="s">
-        <v>583</v>
-      </c>
-      <c r="C54" t="s">
-        <v>690</v>
-      </c>
-      <c r="D54" t="s">
-        <v>580</v>
-      </c>
-      <c r="E54" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>691</v>
-      </c>
-      <c r="B55" t="s">
-        <v>586</v>
-      </c>
-      <c r="C55" t="s">
-        <v>692</v>
-      </c>
-      <c r="D55" t="s">
-        <v>575</v>
-      </c>
-      <c r="E55" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>693</v>
-      </c>
-      <c r="B56" t="s">
-        <v>573</v>
-      </c>
-      <c r="C56" t="s">
-        <v>694</v>
-      </c>
-      <c r="D56" t="s">
-        <v>591</v>
-      </c>
-      <c r="E56" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>695</v>
-      </c>
-      <c r="B57" t="s">
-        <v>594</v>
-      </c>
-      <c r="C57" t="s">
-        <v>696</v>
-      </c>
-      <c r="D57" t="s">
-        <v>575</v>
-      </c>
-      <c r="E57" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>697</v>
-      </c>
-      <c r="B58" t="s">
-        <v>597</v>
-      </c>
-      <c r="C58" t="s">
-        <v>698</v>
-      </c>
-      <c r="D58" t="s">
-        <v>599</v>
-      </c>
-      <c r="E58" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>699</v>
-      </c>
-      <c r="B59" t="s">
-        <v>602</v>
-      </c>
-      <c r="C59" t="s">
-        <v>700</v>
-      </c>
-      <c r="D59" t="s">
-        <v>580</v>
-      </c>
-      <c r="E59" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>701</v>
-      </c>
-      <c r="B60" t="s">
-        <v>573</v>
-      </c>
-      <c r="C60" t="s">
-        <v>702</v>
-      </c>
-      <c r="D60" t="s">
-        <v>575</v>
-      </c>
-      <c r="E60" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>703</v>
-      </c>
-      <c r="B61" t="s">
-        <v>578</v>
-      </c>
-      <c r="C61" t="s">
-        <v>704</v>
-      </c>
-      <c r="D61" t="s">
-        <v>580</v>
-      </c>
-      <c r="E61" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>705</v>
-      </c>
-      <c r="B62" t="s">
-        <v>583</v>
-      </c>
-      <c r="C62" t="s">
-        <v>706</v>
-      </c>
-      <c r="D62" t="s">
-        <v>580</v>
-      </c>
-      <c r="E62" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>707</v>
-      </c>
-      <c r="B63" t="s">
-        <v>586</v>
-      </c>
-      <c r="C63" t="s">
-        <v>708</v>
-      </c>
-      <c r="D63" t="s">
-        <v>575</v>
-      </c>
-      <c r="E63" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>709</v>
-      </c>
-      <c r="B64" t="s">
-        <v>573</v>
-      </c>
-      <c r="C64" t="s">
-        <v>710</v>
-      </c>
-      <c r="D64" t="s">
-        <v>591</v>
-      </c>
-      <c r="E64" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>711</v>
-      </c>
-      <c r="B65" t="s">
-        <v>594</v>
-      </c>
-      <c r="C65" t="s">
-        <v>712</v>
-      </c>
-      <c r="D65" t="s">
-        <v>575</v>
-      </c>
-      <c r="E65" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>713</v>
-      </c>
-      <c r="B66" t="s">
-        <v>597</v>
-      </c>
-      <c r="C66" t="s">
-        <v>714</v>
-      </c>
-      <c r="D66" t="s">
-        <v>599</v>
-      </c>
-      <c r="E66" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>715</v>
-      </c>
-      <c r="B67" t="s">
-        <v>602</v>
-      </c>
-      <c r="C67" t="s">
-        <v>716</v>
-      </c>
-      <c r="D67" t="s">
-        <v>580</v>
-      </c>
-      <c r="E67" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>717</v>
-      </c>
-      <c r="B68" t="s">
-        <v>573</v>
-      </c>
-      <c r="C68" t="s">
-        <v>718</v>
-      </c>
-      <c r="D68" t="s">
-        <v>575</v>
-      </c>
-      <c r="E68" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>719</v>
-      </c>
-      <c r="B69" t="s">
-        <v>578</v>
-      </c>
-      <c r="C69" t="s">
-        <v>720</v>
-      </c>
-      <c r="D69" t="s">
-        <v>580</v>
-      </c>
-      <c r="E69" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>721</v>
-      </c>
-      <c r="B70" t="s">
-        <v>583</v>
-      </c>
-      <c r="C70" t="s">
-        <v>722</v>
-      </c>
-      <c r="D70" t="s">
-        <v>580</v>
-      </c>
-      <c r="E70" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>723</v>
-      </c>
-      <c r="B71" t="s">
-        <v>586</v>
-      </c>
-      <c r="C71" t="s">
-        <v>724</v>
-      </c>
-      <c r="D71" t="s">
-        <v>575</v>
-      </c>
-      <c r="E71" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>725</v>
-      </c>
-      <c r="B72" t="s">
-        <v>573</v>
-      </c>
-      <c r="C72" t="s">
-        <v>726</v>
-      </c>
-      <c r="D72" t="s">
-        <v>591</v>
-      </c>
-      <c r="E72" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>727</v>
-      </c>
-      <c r="B73" t="s">
-        <v>594</v>
-      </c>
-      <c r="C73" t="s">
-        <v>728</v>
-      </c>
-      <c r="D73" t="s">
-        <v>575</v>
-      </c>
-      <c r="E73" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>729</v>
-      </c>
-      <c r="B74" t="s">
-        <v>597</v>
-      </c>
-      <c r="C74" t="s">
-        <v>730</v>
-      </c>
-      <c r="D74" t="s">
-        <v>599</v>
-      </c>
-      <c r="E74" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>731</v>
-      </c>
-      <c r="B75" t="s">
-        <v>602</v>
-      </c>
-      <c r="C75" t="s">
-        <v>732</v>
-      </c>
-      <c r="D75" t="s">
-        <v>580</v>
-      </c>
-      <c r="E75" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>733</v>
-      </c>
-      <c r="B76" t="s">
-        <v>573</v>
-      </c>
-      <c r="C76" t="s">
-        <v>734</v>
-      </c>
-      <c r="D76" t="s">
-        <v>575</v>
-      </c>
-      <c r="E76" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>735</v>
-      </c>
-      <c r="B77" t="s">
-        <v>578</v>
-      </c>
-      <c r="C77" t="s">
-        <v>736</v>
-      </c>
-      <c r="D77" t="s">
-        <v>580</v>
-      </c>
-      <c r="E77" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>737</v>
-      </c>
-      <c r="B78" t="s">
-        <v>583</v>
-      </c>
-      <c r="C78" t="s">
-        <v>738</v>
-      </c>
-      <c r="D78" t="s">
-        <v>580</v>
-      </c>
-      <c r="E78" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>739</v>
-      </c>
-      <c r="B79" t="s">
-        <v>586</v>
-      </c>
-      <c r="C79" t="s">
-        <v>740</v>
-      </c>
-      <c r="D79" t="s">
-        <v>575</v>
-      </c>
-      <c r="E79" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>741</v>
-      </c>
-      <c r="B80" t="s">
-        <v>573</v>
-      </c>
-      <c r="C80" t="s">
-        <v>742</v>
-      </c>
-      <c r="D80" t="s">
-        <v>591</v>
-      </c>
-      <c r="E80" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>743</v>
-      </c>
-      <c r="B81" t="s">
-        <v>594</v>
-      </c>
-      <c r="C81" t="s">
-        <v>744</v>
-      </c>
-      <c r="D81" t="s">
-        <v>575</v>
-      </c>
-      <c r="E81" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>745</v>
-      </c>
-      <c r="B82" t="s">
-        <v>597</v>
-      </c>
-      <c r="C82" t="s">
-        <v>746</v>
-      </c>
-      <c r="D82" t="s">
-        <v>599</v>
-      </c>
-      <c r="E82" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>747</v>
-      </c>
-      <c r="B83" t="s">
-        <v>602</v>
-      </c>
-      <c r="C83" t="s">
-        <v>748</v>
-      </c>
-      <c r="D83" t="s">
-        <v>580</v>
-      </c>
-      <c r="E83" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>749</v>
-      </c>
-      <c r="B84" t="s">
-        <v>573</v>
-      </c>
-      <c r="C84" t="s">
-        <v>750</v>
-      </c>
-      <c r="D84" t="s">
-        <v>575</v>
-      </c>
-      <c r="E84" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>751</v>
-      </c>
-      <c r="B85" t="s">
-        <v>578</v>
-      </c>
-      <c r="C85" t="s">
-        <v>752</v>
-      </c>
-      <c r="D85" t="s">
-        <v>580</v>
-      </c>
-      <c r="E85" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>753</v>
-      </c>
-      <c r="B86" t="s">
-        <v>583</v>
-      </c>
-      <c r="C86" t="s">
-        <v>754</v>
-      </c>
-      <c r="D86" t="s">
-        <v>580</v>
-      </c>
-      <c r="E86" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>755</v>
-      </c>
-      <c r="B87" t="s">
-        <v>586</v>
-      </c>
-      <c r="C87" t="s">
-        <v>756</v>
-      </c>
-      <c r="D87" t="s">
-        <v>575</v>
-      </c>
-      <c r="E87" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>757</v>
-      </c>
-      <c r="B88" t="s">
-        <v>573</v>
-      </c>
-      <c r="C88" t="s">
-        <v>758</v>
-      </c>
-      <c r="D88" t="s">
-        <v>591</v>
-      </c>
-      <c r="E88" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>759</v>
-      </c>
-      <c r="B89" t="s">
-        <v>594</v>
-      </c>
-      <c r="C89" t="s">
-        <v>760</v>
-      </c>
-      <c r="D89" t="s">
-        <v>575</v>
-      </c>
-      <c r="E89" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>761</v>
-      </c>
-      <c r="B90" t="s">
-        <v>597</v>
-      </c>
-      <c r="C90" t="s">
-        <v>762</v>
-      </c>
-      <c r="D90" t="s">
-        <v>599</v>
-      </c>
-      <c r="E90" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>763</v>
-      </c>
-      <c r="B91" t="s">
-        <v>602</v>
-      </c>
-      <c r="C91" t="s">
-        <v>764</v>
-      </c>
-      <c r="D91" t="s">
-        <v>580</v>
-      </c>
-      <c r="E91" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>765</v>
-      </c>
-      <c r="B92" t="s">
-        <v>573</v>
-      </c>
-      <c r="C92" t="s">
-        <v>766</v>
-      </c>
-      <c r="D92" t="s">
-        <v>575</v>
-      </c>
-      <c r="E92" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>767</v>
-      </c>
-      <c r="B93" t="s">
-        <v>578</v>
-      </c>
-      <c r="C93" t="s">
-        <v>768</v>
-      </c>
-      <c r="D93" t="s">
-        <v>580</v>
-      </c>
-      <c r="E93" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>769</v>
-      </c>
-      <c r="B94" t="s">
-        <v>583</v>
-      </c>
-      <c r="C94" t="s">
-        <v>770</v>
-      </c>
-      <c r="D94" t="s">
-        <v>580</v>
-      </c>
-      <c r="E94" t="s">
-        <v>775</v>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -12506,507 +12764,507 @@
     </row>
     <row r="2" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>853</v>
+        <v>762</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>851</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>766</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>702</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>654</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>694</v>
+        <v>641</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>662</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>638</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>750</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>686</v>
+        <v>637</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>718</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>678</v>
+        <v>633</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>742</v>
+        <v>665</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>646</v>
+        <v>617</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>726</v>
+        <v>657</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>758</v>
+        <v>673</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>734</v>
+        <v>661</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>710</v>
+        <v>649</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>670</v>
+        <v>629</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>628</v>
+        <v>608</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>692</v>
+        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>644</v>
+        <v>616</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>740</v>
+        <v>664</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>708</v>
+        <v>648</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>756</v>
+        <v>672</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>676</v>
+        <v>632</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>724</v>
+        <v>656</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>660</v>
+        <v>624</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>690</v>
+        <v>639</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>674</v>
+        <v>631</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>722</v>
+        <v>655</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>706</v>
+        <v>647</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>770</v>
+        <v>679</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>658</v>
+        <v>623</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>738</v>
+        <v>663</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>626</v>
+        <v>607</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>754</v>
+        <v>671</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>760</v>
+        <v>674</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>728</v>
+        <v>658</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>664</v>
+        <v>626</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>680</v>
+        <v>634</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
-        <v>712</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>632</v>
+        <v>610</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
-        <v>744</v>
+        <v>666</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>648</v>
+        <v>618</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
-        <v>696</v>
+        <v>642</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
-        <v>650</v>
+        <v>619</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
-        <v>762</v>
+        <v>675</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
-        <v>746</v>
+        <v>667</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
-        <v>698</v>
+        <v>643</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
-        <v>714</v>
+        <v>651</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
-        <v>634</v>
+        <v>611</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
-        <v>666</v>
+        <v>627</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
-        <v>682</v>
+        <v>635</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
-        <v>730</v>
+        <v>659</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
-        <v>716</v>
+        <v>652</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
-        <v>764</v>
+        <v>676</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
-        <v>652</v>
+        <v>620</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
-        <v>732</v>
+        <v>660</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
-        <v>748</v>
+        <v>668</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
-        <v>668</v>
+        <v>628</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="14" t="s">
-        <v>700</v>
+        <v>644</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="14" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="14" t="s">
-        <v>684</v>
+        <v>636</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="14" t="s">
-        <v>636</v>
+        <v>612</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
-        <v>720</v>
+        <v>654</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
-        <v>688</v>
+        <v>638</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
-        <v>640</v>
+        <v>614</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="14" t="s">
-        <v>736</v>
+        <v>662</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
-        <v>768</v>
+        <v>678</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
-        <v>672</v>
+        <v>630</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
-        <v>656</v>
+        <v>622</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
-        <v>752</v>
+        <v>670</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
-        <v>704</v>
+        <v>646</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
-        <v>852</v>
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -17586,14 +17844,14 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G199">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
       <formula>0.05</formula>
       <formula>0.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17623,7 +17881,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>856</v>
+        <v>765</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -17631,10 +17889,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>854</v>
+        <v>763</v>
       </c>
       <c r="C3" t="s">
-        <v>855</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -19773,7 +20031,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="13" t="s">
-        <v>852</v>
+        <v>761</v>
       </c>
       <c r="B198">
         <v>16440</v>
@@ -19807,11 +20065,11 @@
     </row>
     <row r="2" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>777</v>
+        <v>686</v>
       </c>
       <c r="B2" s="6"/>
       <c r="D2" s="5" t="s">
-        <v>850</v>
+        <v>759</v>
       </c>
       <c r="E2" s="6"/>
     </row>
@@ -19831,7 +20089,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>778</v>
+        <v>687</v>
       </c>
       <c r="B4" s="2">
         <v>12.5</v>
@@ -19849,7 +20107,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>779</v>
+        <v>688</v>
       </c>
       <c r="B6" s="2">
         <v>15</v>
@@ -19858,7 +20116,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>780</v>
+        <v>689</v>
       </c>
       <c r="B7" s="2">
         <v>97</v>
@@ -19867,7 +20125,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>781</v>
+        <v>690</v>
       </c>
       <c r="B8" s="2">
         <v>21</v>
@@ -19876,7 +20134,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>782</v>
+        <v>691</v>
       </c>
       <c r="B9" s="2">
         <v>18</v>
@@ -19912,7 +20170,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>783</v>
+        <v>692</v>
       </c>
       <c r="B13" s="2">
         <v>34</v>
@@ -19921,7 +20179,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>784</v>
+        <v>693</v>
       </c>
       <c r="B14" s="2">
         <v>28.5</v>
@@ -19930,7 +20188,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>785</v>
+        <v>694</v>
       </c>
       <c r="B15" s="2">
         <v>12.75</v>
@@ -19966,7 +20224,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>786</v>
+        <v>695</v>
       </c>
       <c r="B19" s="2">
         <v>23.5</v>
@@ -19975,7 +20233,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>787</v>
+        <v>696</v>
       </c>
       <c r="B20" s="2">
         <v>97.5</v>
@@ -19984,7 +20242,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>788</v>
+        <v>697</v>
       </c>
       <c r="B21" s="2">
         <v>40</v>
@@ -19993,7 +20251,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>789</v>
+        <v>698</v>
       </c>
       <c r="B22" s="2">
         <v>32</v>
@@ -20002,7 +20260,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>790</v>
+        <v>699</v>
       </c>
       <c r="B23" s="2">
         <v>15.5</v>
@@ -20011,7 +20269,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>791</v>
+        <v>700</v>
       </c>
       <c r="B24" s="2">
         <v>53</v>
@@ -20020,7 +20278,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>792</v>
+        <v>701</v>
       </c>
       <c r="B25" s="2">
         <v>30</v>
@@ -20029,7 +20287,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>793</v>
+        <v>702</v>
       </c>
       <c r="B26" s="2">
         <v>18.399999999999999</v>
@@ -20038,7 +20296,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>794</v>
+        <v>703</v>
       </c>
       <c r="B27" s="2">
         <v>38</v>
@@ -20047,7 +20305,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>795</v>
+        <v>704</v>
       </c>
       <c r="B28" s="2">
         <v>120</v>
@@ -20056,7 +20314,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>796</v>
+        <v>705</v>
       </c>
       <c r="B29" s="2">
         <v>5.5</v>
@@ -20065,7 +20323,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>797</v>
+        <v>706</v>
       </c>
       <c r="B30" s="2">
         <v>123.79</v>
@@ -20074,7 +20332,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>798</v>
+        <v>707</v>
       </c>
       <c r="B31" s="2">
         <v>38</v>
@@ -20083,7 +20341,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>799</v>
+        <v>708</v>
       </c>
       <c r="B32" s="2">
         <v>36.5</v>
@@ -20092,7 +20350,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>800</v>
+        <v>709</v>
       </c>
       <c r="B33" s="2">
         <v>21.5</v>
@@ -20101,7 +20359,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>801</v>
+        <v>710</v>
       </c>
       <c r="B34" s="2">
         <v>18</v>
@@ -20119,7 +20377,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>802</v>
+        <v>711</v>
       </c>
       <c r="B36" s="2">
         <v>17</v>
@@ -20128,7 +20386,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>803</v>
+        <v>712</v>
       </c>
       <c r="B37" s="2">
         <v>25</v>
@@ -20137,7 +20395,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>804</v>
+        <v>713</v>
       </c>
       <c r="B38" s="2">
         <v>9.1999999999999993</v>
@@ -20146,7 +20404,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>805</v>
+        <v>714</v>
       </c>
       <c r="B39" s="2">
         <v>18.399999999999999</v>
@@ -20155,7 +20413,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>806</v>
+        <v>715</v>
       </c>
       <c r="B40" s="2">
         <v>46</v>
@@ -20164,7 +20422,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>807</v>
+        <v>716</v>
       </c>
       <c r="B41" s="2">
         <v>16</v>
@@ -20173,7 +20431,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>808</v>
+        <v>717</v>
       </c>
       <c r="B42" s="2">
         <v>55</v>
@@ -20182,7 +20440,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>809</v>
+        <v>718</v>
       </c>
       <c r="B43" s="2">
         <v>30</v>
@@ -20191,7 +20449,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>810</v>
+        <v>719</v>
       </c>
       <c r="B44" s="2">
         <v>97</v>
@@ -20200,7 +20458,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>811</v>
+        <v>720</v>
       </c>
       <c r="B45" s="2">
         <v>39</v>
@@ -20209,7 +20467,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>812</v>
+        <v>721</v>
       </c>
       <c r="B46" s="2">
         <v>19</v>
@@ -20218,7 +20476,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>813</v>
+        <v>722</v>
       </c>
       <c r="B47" s="2">
         <v>38</v>
@@ -20227,7 +20485,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>814</v>
+        <v>723</v>
       </c>
       <c r="B48" s="2">
         <v>18</v>
@@ -20236,7 +20494,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>815</v>
+        <v>724</v>
       </c>
       <c r="B49" s="2">
         <v>28.5</v>
@@ -20245,7 +20503,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>816</v>
+        <v>725</v>
       </c>
       <c r="B50" s="2">
         <v>12.75</v>
@@ -20254,7 +20512,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>817</v>
+        <v>726</v>
       </c>
       <c r="B51" s="2">
         <v>32</v>
@@ -20263,7 +20521,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>818</v>
+        <v>727</v>
       </c>
       <c r="B52" s="2">
         <v>34</v>
@@ -20272,7 +20530,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>819</v>
+        <v>728</v>
       </c>
       <c r="B53" s="2">
         <v>15.5</v>
@@ -20281,7 +20539,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>820</v>
+        <v>729</v>
       </c>
       <c r="B54" s="2">
         <v>25</v>
@@ -20290,7 +20548,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>821</v>
+        <v>730</v>
       </c>
       <c r="B55" s="2">
         <v>81</v>
@@ -20299,7 +20557,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>822</v>
+        <v>731</v>
       </c>
       <c r="B56" s="2">
         <v>24</v>
@@ -20308,7 +20566,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>823</v>
+        <v>732</v>
       </c>
       <c r="B57" s="2">
         <v>21</v>
@@ -20317,7 +20575,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>824</v>
+        <v>733</v>
       </c>
       <c r="B58" s="2">
         <v>32.799999999999997</v>
@@ -20326,7 +20584,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>825</v>
+        <v>734</v>
       </c>
       <c r="B59" s="2">
         <v>19</v>
@@ -20335,7 +20593,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>826</v>
+        <v>735</v>
       </c>
       <c r="B60" s="2">
         <v>36</v>
@@ -20344,7 +20602,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>827</v>
+        <v>736</v>
       </c>
       <c r="B61" s="2">
         <v>26</v>
@@ -20353,7 +20611,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>828</v>
+        <v>737</v>
       </c>
       <c r="B62" s="2">
         <v>18</v>
@@ -20362,7 +20620,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>829</v>
+        <v>738</v>
       </c>
       <c r="B63" s="2">
         <v>6.5</v>
@@ -20371,7 +20629,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>830</v>
+        <v>739</v>
       </c>
       <c r="B64" s="2">
         <v>24</v>
@@ -20380,7 +20638,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>831</v>
+        <v>740</v>
       </c>
       <c r="B65" s="2">
         <v>55</v>
@@ -20389,7 +20647,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>832</v>
+        <v>741</v>
       </c>
       <c r="B66" s="2">
         <v>7.45</v>
@@ -20398,7 +20656,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>833</v>
+        <v>742</v>
       </c>
       <c r="B67" s="2">
         <v>25</v>
@@ -20407,7 +20665,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>834</v>
+        <v>743</v>
       </c>
       <c r="B68" s="2">
         <v>15</v>
@@ -20416,7 +20674,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>835</v>
+        <v>744</v>
       </c>
       <c r="B69" s="2">
         <v>38</v>
@@ -20425,7 +20683,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>836</v>
+        <v>745</v>
       </c>
       <c r="B70" s="2">
         <v>12.5</v>
@@ -20434,7 +20692,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>837</v>
+        <v>746</v>
       </c>
       <c r="B71" s="2">
         <v>100</v>
@@ -20443,7 +20701,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>838</v>
+        <v>747</v>
       </c>
       <c r="B72" s="2">
         <v>26</v>
@@ -20452,7 +20710,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>839</v>
+        <v>748</v>
       </c>
       <c r="B73" s="2">
         <v>21.5</v>
@@ -20461,7 +20719,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>840</v>
+        <v>749</v>
       </c>
       <c r="B74" s="2">
         <v>26</v>
@@ -20470,7 +20728,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>841</v>
+        <v>750</v>
       </c>
       <c r="B75" s="2">
         <v>19.5</v>
@@ -20479,7 +20737,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>842</v>
+        <v>751</v>
       </c>
       <c r="B76" s="2">
         <v>4.5</v>
@@ -20488,7 +20746,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>843</v>
+        <v>752</v>
       </c>
       <c r="B77" s="2">
         <v>21.35</v>
@@ -20497,7 +20755,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>844</v>
+        <v>753</v>
       </c>
       <c r="B78" s="2">
         <v>21.5</v>
@@ -20506,7 +20764,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>845</v>
+        <v>754</v>
       </c>
       <c r="B79" s="2">
         <v>150</v>
@@ -20515,7 +20773,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>846</v>
+        <v>755</v>
       </c>
       <c r="B80" s="2">
         <v>40</v>
@@ -20524,7 +20782,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>847</v>
+        <v>756</v>
       </c>
       <c r="B81" s="2">
         <v>18</v>
@@ -20533,7 +20791,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>848</v>
+        <v>757</v>
       </c>
       <c r="B82" s="2">
         <v>2.5</v>
@@ -20542,7 +20800,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>849</v>
+        <v>758</v>
       </c>
       <c r="B83" s="2">
         <v>7.75</v>
